--- a/research/traditional_assets/database/data/taiwan/taiwan_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07484350764588704</v>
+        <v>0.07472982063059527</v>
       </c>
       <c r="C2">
-        <v>57.2905782018468</v>
+        <v>56.8904952960058</v>
       </c>
       <c r="D2">
-        <v>51.8905782018468</v>
+        <v>52.0944952960058</v>
       </c>
       <c r="E2">
-        <v>-18.3</v>
+        <v>-17.696</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6040000000000001</v>
       </c>
       <c r="G2">
         <v>5.4</v>
@@ -1451,28 +1451,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0303812</v>
       </c>
       <c r="N2">
-        <v>3.014081632653062</v>
+        <v>2.983700432653062</v>
       </c>
       <c r="O2">
-        <v>0.6028163265306123</v>
+        <v>0.5967400865306124</v>
       </c>
       <c r="P2">
-        <v>2.411265306122449</v>
+        <v>2.386960346122449</v>
       </c>
       <c r="Q2">
-        <v>6.601265306122449</v>
+        <v>6.576960346122449</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07484350764588704</v>
+        <v>0.07507820265716694</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5706866652781318</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>99.20877492176284</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07472982063059527</v>
+        <v>0.07461613361530349</v>
       </c>
       <c r="C3">
-        <v>56.8904952960058</v>
+        <v>56.49202140031944</v>
       </c>
       <c r="D3">
-        <v>52.0944952960058</v>
+        <v>52.30002140031944</v>
       </c>
       <c r="E3">
-        <v>-17.696</v>
+        <v>-17.092</v>
       </c>
       <c r="F3">
-        <v>0.6040000000000001</v>
+        <v>1.208</v>
       </c>
       <c r="G3">
         <v>5.4</v>
@@ -1533,28 +1533,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M3">
-        <v>0.0303812</v>
+        <v>0.06076240000000001</v>
       </c>
       <c r="N3">
-        <v>2.983700432653062</v>
+        <v>2.953319232653061</v>
       </c>
       <c r="O3">
-        <v>0.5967400865306124</v>
+        <v>0.5906638465306123</v>
       </c>
       <c r="P3">
-        <v>2.386960346122449</v>
+        <v>2.362655386122449</v>
       </c>
       <c r="Q3">
-        <v>6.576960346122449</v>
+        <v>6.552655386122448</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07507820265716694</v>
+        <v>0.07531768736255459</v>
       </c>
       <c r="T3">
-        <v>0.5706866652781318</v>
+        <v>0.5753546679387848</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>99.20877492176284</v>
+        <v>49.60438746088141</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07461613361530349</v>
+        <v>0.07450244660001172</v>
       </c>
       <c r="C4">
-        <v>56.49202140031944</v>
+        <v>56.09517563408764</v>
       </c>
       <c r="D4">
-        <v>52.30002140031944</v>
+        <v>52.50717563408764</v>
       </c>
       <c r="E4">
-        <v>-17.092</v>
+        <v>-16.488</v>
       </c>
       <c r="F4">
-        <v>1.208</v>
+        <v>1.812</v>
       </c>
       <c r="G4">
         <v>5.4</v>
@@ -1615,28 +1615,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M4">
-        <v>0.06076240000000001</v>
+        <v>0.09114359999999999</v>
       </c>
       <c r="N4">
-        <v>2.953319232653061</v>
+        <v>2.922938032653061</v>
       </c>
       <c r="O4">
-        <v>0.5906638465306123</v>
+        <v>0.5845876065306123</v>
       </c>
       <c r="P4">
-        <v>2.362655386122449</v>
+        <v>2.338350426122449</v>
       </c>
       <c r="Q4">
-        <v>6.552655386122448</v>
+        <v>6.528350426122449</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07531768736255459</v>
+        <v>0.07556210989691929</v>
       </c>
       <c r="T4">
-        <v>0.5753546679387848</v>
+        <v>0.5801189180769769</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.60438746088141</v>
+        <v>33.06959164058762</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07450244660001172</v>
+        <v>0.07438875958471994</v>
       </c>
       <c r="C5">
-        <v>56.09517563408764</v>
+        <v>55.69997742073218</v>
       </c>
       <c r="D5">
-        <v>52.50717563408764</v>
+        <v>52.71597742073218</v>
       </c>
       <c r="E5">
-        <v>-16.488</v>
+        <v>-15.884</v>
       </c>
       <c r="F5">
-        <v>1.812</v>
+        <v>2.416</v>
       </c>
       <c r="G5">
         <v>5.4</v>
@@ -1697,28 +1697,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M5">
-        <v>0.09114359999999999</v>
+        <v>0.1215248</v>
       </c>
       <c r="N5">
-        <v>2.922938032653061</v>
+        <v>2.892556832653062</v>
       </c>
       <c r="O5">
-        <v>0.5845876065306123</v>
+        <v>0.5785113665306123</v>
       </c>
       <c r="P5">
-        <v>2.338350426122449</v>
+        <v>2.314045466122449</v>
       </c>
       <c r="Q5">
-        <v>6.528350426122449</v>
+        <v>6.504045466122449</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07556210989691929</v>
+        <v>0.07581162456741661</v>
       </c>
       <c r="T5">
-        <v>0.5801189180769769</v>
+        <v>0.5849824234263816</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.06959164058762</v>
+        <v>24.80219373044071</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07438875958471994</v>
+        <v>0.07427507256942815</v>
       </c>
       <c r="C6">
-        <v>55.69997742073218</v>
+        <v>55.30644649386762</v>
       </c>
       <c r="D6">
-        <v>52.71597742073218</v>
+        <v>52.92644649386762</v>
       </c>
       <c r="E6">
-        <v>-15.884</v>
+        <v>-15.28</v>
       </c>
       <c r="F6">
-        <v>2.416</v>
+        <v>3.02</v>
       </c>
       <c r="G6">
         <v>5.4</v>
@@ -1779,28 +1779,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M6">
-        <v>0.1215248</v>
+        <v>0.151906</v>
       </c>
       <c r="N6">
-        <v>2.892556832653062</v>
+        <v>2.862175632653062</v>
       </c>
       <c r="O6">
-        <v>0.5785113665306123</v>
+        <v>0.5724351265306123</v>
       </c>
       <c r="P6">
-        <v>2.314045466122449</v>
+        <v>2.289740506122449</v>
       </c>
       <c r="Q6">
-        <v>6.504045466122449</v>
+        <v>6.479740506122448</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07581162456741661</v>
+        <v>0.07606639217834543</v>
       </c>
       <c r="T6">
-        <v>0.5849824234263816</v>
+        <v>0.5899483183620893</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.80219373044071</v>
+        <v>19.84175498435257</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07427507256942815</v>
+        <v>0.0741613855541364</v>
       </c>
       <c r="C7">
-        <v>55.30644649386762</v>
+        <v>54.91460290351839</v>
       </c>
       <c r="D7">
-        <v>52.92644649386762</v>
+        <v>53.13860290351839</v>
       </c>
       <c r="E7">
-        <v>-15.28</v>
+        <v>-14.676</v>
       </c>
       <c r="F7">
-        <v>3.02</v>
+        <v>3.624000000000001</v>
       </c>
       <c r="G7">
         <v>5.4</v>
@@ -1861,28 +1861,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M7">
-        <v>0.151906</v>
+        <v>0.1822872</v>
       </c>
       <c r="N7">
-        <v>2.862175632653062</v>
+        <v>2.831794432653061</v>
       </c>
       <c r="O7">
-        <v>0.5724351265306123</v>
+        <v>0.5663588865306123</v>
       </c>
       <c r="P7">
-        <v>2.289740506122449</v>
+        <v>2.265435546122449</v>
       </c>
       <c r="Q7">
-        <v>6.479740506122448</v>
+        <v>6.455435546122448</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07606639217834543</v>
+        <v>0.07632658037674085</v>
       </c>
       <c r="T7">
-        <v>0.5899483183620893</v>
+        <v>0.5950198706368549</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.84175498435257</v>
+        <v>16.53479582029381</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0741613855541364</v>
+        <v>0.07404769853884462</v>
       </c>
       <c r="C8">
-        <v>54.91460290351839</v>
+        <v>54.52446702248612</v>
       </c>
       <c r="D8">
-        <v>53.13860290351839</v>
+        <v>53.35246702248612</v>
       </c>
       <c r="E8">
-        <v>-14.676</v>
+        <v>-14.072</v>
       </c>
       <c r="F8">
-        <v>3.624</v>
+        <v>4.228</v>
       </c>
       <c r="G8">
         <v>5.4</v>
@@ -1943,28 +1943,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M8">
-        <v>0.1822872</v>
+        <v>0.2126684</v>
       </c>
       <c r="N8">
-        <v>2.831794432653061</v>
+        <v>2.801413232653061</v>
       </c>
       <c r="O8">
-        <v>0.5663588865306123</v>
+        <v>0.5602826465306123</v>
       </c>
       <c r="P8">
-        <v>2.265435546122449</v>
+        <v>2.241130586122449</v>
       </c>
       <c r="Q8">
-        <v>6.455435546122448</v>
+        <v>6.431130586122449</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07632658037674085</v>
+        <v>0.07659236402026304</v>
       </c>
       <c r="T8">
-        <v>0.5950198706368549</v>
+        <v>0.6002004885519379</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.53479582029381</v>
+        <v>14.17268213168041</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07404769853884462</v>
+        <v>0.07403001152355286</v>
       </c>
       <c r="C9">
-        <v>54.52446702248612</v>
+        <v>53.95389406870934</v>
       </c>
       <c r="D9">
-        <v>53.35246702248612</v>
+        <v>53.38589406870934</v>
       </c>
       <c r="E9">
-        <v>-14.072</v>
+        <v>-13.468</v>
       </c>
       <c r="F9">
-        <v>4.228000000000001</v>
+        <v>4.832000000000001</v>
       </c>
       <c r="G9">
         <v>5.4</v>
@@ -2025,45 +2025,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M9">
-        <v>0.2126684</v>
+        <v>0.2502976</v>
       </c>
       <c r="N9">
-        <v>2.801413232653061</v>
+        <v>2.763784032653061</v>
       </c>
       <c r="O9">
-        <v>0.5602826465306123</v>
+        <v>0.5527568065306123</v>
       </c>
       <c r="P9">
-        <v>2.241130586122449</v>
+        <v>2.211027226122449</v>
       </c>
       <c r="Q9">
-        <v>6.431130586122449</v>
+        <v>6.401027226122449</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07659236402026304</v>
+        <v>0.07686392556907919</v>
       </c>
       <c r="T9">
-        <v>0.6002004885519379</v>
+        <v>0.6054937285956096</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.17268213168041</v>
+        <v>12.04199174364062</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07403001152355286</v>
+        <v>0.07392832450826106</v>
       </c>
       <c r="C10">
-        <v>53.95389406870934</v>
+        <v>53.54289000150786</v>
       </c>
       <c r="D10">
-        <v>53.38589406870934</v>
+        <v>53.57889000150786</v>
       </c>
       <c r="E10">
-        <v>-13.468</v>
+        <v>-12.864</v>
       </c>
       <c r="F10">
-        <v>4.832000000000001</v>
+        <v>5.436</v>
       </c>
       <c r="G10">
         <v>5.4</v>
@@ -2107,28 +2107,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M10">
-        <v>0.2502976</v>
+        <v>0.2815848</v>
       </c>
       <c r="N10">
-        <v>2.763784032653061</v>
+        <v>2.732496832653061</v>
       </c>
       <c r="O10">
-        <v>0.5527568065306123</v>
+        <v>0.5464993665306123</v>
       </c>
       <c r="P10">
-        <v>2.211027226122449</v>
+        <v>2.185997466122449</v>
       </c>
       <c r="Q10">
-        <v>6.401027226122449</v>
+        <v>6.375997466122449</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07686392556907919</v>
+        <v>0.07714145550358359</v>
       </c>
       <c r="T10">
-        <v>0.6054937285956096</v>
+        <v>0.610903303585296</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.04199174364062</v>
+        <v>10.70399266101388</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07392832450826106</v>
+        <v>0.07396263749296932</v>
       </c>
       <c r="C11">
-        <v>53.54289000150786</v>
+        <v>52.87361019120011</v>
       </c>
       <c r="D11">
-        <v>53.57889000150786</v>
+        <v>53.51361019120011</v>
       </c>
       <c r="E11">
-        <v>-12.864</v>
+        <v>-12.26</v>
       </c>
       <c r="F11">
-        <v>5.436</v>
+        <v>6.04</v>
       </c>
       <c r="G11">
         <v>5.4</v>
@@ -2189,45 +2189,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M11">
-        <v>0.2815848</v>
+        <v>0.32314</v>
       </c>
       <c r="N11">
-        <v>2.732496832653061</v>
+        <v>2.690941632653062</v>
       </c>
       <c r="O11">
-        <v>0.5464993665306123</v>
+        <v>0.5381883265306123</v>
       </c>
       <c r="P11">
-        <v>2.185997466122449</v>
+        <v>2.152753306122449</v>
       </c>
       <c r="Q11">
-        <v>6.375997466122449</v>
+        <v>6.342753306122448</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07714145550358359</v>
+        <v>0.07742515276996589</v>
       </c>
       <c r="T11">
-        <v>0.610903303585296</v>
+        <v>0.616433091352531</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.70399266101388</v>
+        <v>9.327479212270415</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07396263749296932</v>
+        <v>0.07387455047767753</v>
       </c>
       <c r="C12">
-        <v>52.87361019120011</v>
+        <v>52.43751507726333</v>
       </c>
       <c r="D12">
-        <v>53.51361019120011</v>
+        <v>53.68151507726333</v>
       </c>
       <c r="E12">
-        <v>-12.26</v>
+        <v>-11.656</v>
       </c>
       <c r="F12">
-        <v>6.040000000000001</v>
+        <v>6.644000000000001</v>
       </c>
       <c r="G12">
         <v>5.4</v>
@@ -2271,28 +2271,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M12">
-        <v>0.32314</v>
+        <v>0.355454</v>
       </c>
       <c r="N12">
-        <v>2.690941632653062</v>
+        <v>2.658627632653062</v>
       </c>
       <c r="O12">
-        <v>0.5381883265306123</v>
+        <v>0.5317255265306123</v>
       </c>
       <c r="P12">
-        <v>2.152753306122449</v>
+        <v>2.126902106122449</v>
       </c>
       <c r="Q12">
-        <v>6.342753306122448</v>
+        <v>6.316902106122448</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07742515276996589</v>
+        <v>0.07771522525581745</v>
       </c>
       <c r="T12">
-        <v>0.6164330913525312</v>
+        <v>0.6220871440134119</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.327479212270413</v>
+        <v>8.479526556609466</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07387455047767753</v>
+        <v>0.07378646346238575</v>
       </c>
       <c r="C13">
-        <v>52.43751507726333</v>
+        <v>52.00247692004323</v>
       </c>
       <c r="D13">
-        <v>53.68151507726333</v>
+        <v>53.85047692004323</v>
       </c>
       <c r="E13">
-        <v>-11.656</v>
+        <v>-11.052</v>
       </c>
       <c r="F13">
-        <v>6.644000000000001</v>
+        <v>7.248</v>
       </c>
       <c r="G13">
         <v>5.4</v>
@@ -2353,28 +2353,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M13">
-        <v>0.355454</v>
+        <v>0.387768</v>
       </c>
       <c r="N13">
-        <v>2.658627632653062</v>
+        <v>2.626313632653062</v>
       </c>
       <c r="O13">
-        <v>0.5317255265306123</v>
+        <v>0.5252627265306123</v>
       </c>
       <c r="P13">
-        <v>2.126902106122449</v>
+        <v>2.101050906122449</v>
       </c>
       <c r="Q13">
-        <v>6.316902106122448</v>
+        <v>6.291050906122448</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07771522525581745</v>
+        <v>0.07801189029816563</v>
       </c>
       <c r="T13">
-        <v>0.6220871440134119</v>
+        <v>0.627869697871131</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.479526556609466</v>
+        <v>7.772899343558678</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07378646346238575</v>
+        <v>0.07378157644709399</v>
       </c>
       <c r="C14">
-        <v>52.00247692004323</v>
+        <v>51.4078819692789</v>
       </c>
       <c r="D14">
-        <v>53.85047692004323</v>
+        <v>53.85988196927891</v>
       </c>
       <c r="E14">
-        <v>-11.052</v>
+        <v>-10.448</v>
       </c>
       <c r="F14">
-        <v>7.248</v>
+        <v>7.852000000000001</v>
       </c>
       <c r="G14">
         <v>5.4</v>
@@ -2435,45 +2435,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M14">
-        <v>0.387768</v>
+        <v>0.4263636000000001</v>
       </c>
       <c r="N14">
-        <v>2.626313632653062</v>
+        <v>2.587718032653061</v>
       </c>
       <c r="O14">
-        <v>0.5252627265306123</v>
+        <v>0.5175436065306123</v>
       </c>
       <c r="P14">
-        <v>2.101050906122449</v>
+        <v>2.070174426122449</v>
       </c>
       <c r="Q14">
-        <v>6.291050906122448</v>
+        <v>6.260174426122449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07801189029816563</v>
+        <v>0.0783153752265448</v>
       </c>
       <c r="T14">
-        <v>0.627869697871131</v>
+        <v>0.6337851840014411</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.772899343558678</v>
+        <v>7.069275221086089</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07378157644709399</v>
+        <v>0.07369988943180221</v>
       </c>
       <c r="C15">
-        <v>51.4078819692789</v>
+        <v>50.96157625021117</v>
       </c>
       <c r="D15">
-        <v>53.85988196927891</v>
+        <v>54.01757625021118</v>
       </c>
       <c r="E15">
-        <v>-10.448</v>
+        <v>-9.843999999999999</v>
       </c>
       <c r="F15">
-        <v>7.852000000000001</v>
+        <v>8.456000000000001</v>
       </c>
       <c r="G15">
         <v>5.4</v>
@@ -2517,28 +2517,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M15">
-        <v>0.4263636000000001</v>
+        <v>0.4591608000000001</v>
       </c>
       <c r="N15">
-        <v>2.587718032653061</v>
+        <v>2.554920832653061</v>
       </c>
       <c r="O15">
-        <v>0.5175436065306123</v>
+        <v>0.5109841665306123</v>
       </c>
       <c r="P15">
-        <v>2.070174426122449</v>
+        <v>2.043936666122449</v>
       </c>
       <c r="Q15">
-        <v>6.260174426122449</v>
+        <v>6.233936666122449</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0783153752265448</v>
+        <v>0.07862591794395606</v>
       </c>
       <c r="T15">
-        <v>0.6337851840014411</v>
+        <v>0.6398382395766424</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.069275221086089</v>
+        <v>6.564326991008511</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07369988943180221</v>
+        <v>0.07361820241651044</v>
       </c>
       <c r="C16">
-        <v>50.96157625021117</v>
+        <v>50.51619665677477</v>
       </c>
       <c r="D16">
-        <v>54.01757625021118</v>
+        <v>54.17619665677477</v>
       </c>
       <c r="E16">
-        <v>-9.843999999999999</v>
+        <v>-9.239999999999998</v>
       </c>
       <c r="F16">
-        <v>8.456000000000001</v>
+        <v>9.060000000000002</v>
       </c>
       <c r="G16">
         <v>5.4</v>
@@ -2599,28 +2599,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M16">
-        <v>0.4591608000000001</v>
+        <v>0.4919580000000001</v>
       </c>
       <c r="N16">
-        <v>2.554920832653061</v>
+        <v>2.522123632653061</v>
       </c>
       <c r="O16">
-        <v>0.5109841665306123</v>
+        <v>0.5044247265306122</v>
       </c>
       <c r="P16">
-        <v>2.043936666122449</v>
+        <v>2.017698906122449</v>
       </c>
       <c r="Q16">
-        <v>6.233936666122449</v>
+        <v>6.207698906122449</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07862591794395606</v>
+        <v>0.07894376754883581</v>
       </c>
       <c r="T16">
-        <v>0.6398382395766424</v>
+        <v>0.6460337199889071</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.564326991008511</v>
+        <v>6.126705191607943</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07361820241651043</v>
+        <v>0.07366451540121864</v>
       </c>
       <c r="C17">
-        <v>50.5161966567748</v>
+        <v>49.82215161808719</v>
       </c>
       <c r="D17">
-        <v>54.1761966567748</v>
+        <v>54.08615161808719</v>
       </c>
       <c r="E17">
-        <v>-9.24</v>
+        <v>-8.635999999999999</v>
       </c>
       <c r="F17">
-        <v>9.06</v>
+        <v>9.664000000000001</v>
       </c>
       <c r="G17">
         <v>5.4</v>
@@ -2681,45 +2681,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M17">
-        <v>0.4919580000000001</v>
+        <v>0.5344192000000001</v>
       </c>
       <c r="N17">
-        <v>2.522123632653062</v>
+        <v>2.479662432653061</v>
       </c>
       <c r="O17">
-        <v>0.5044247265306123</v>
+        <v>0.4959324865306123</v>
       </c>
       <c r="P17">
-        <v>2.017698906122449</v>
+        <v>1.983729946122449</v>
       </c>
       <c r="Q17">
-        <v>6.207698906122449</v>
+        <v>6.173729946122449</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07894376754883581</v>
+        <v>0.07926918500145078</v>
       </c>
       <c r="T17">
-        <v>0.6460337199889071</v>
+        <v>0.6523767118395591</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.126705191607945</v>
+        <v>5.639920183730414</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07366451540121864</v>
+        <v>0.07359082838592687</v>
       </c>
       <c r="C18">
-        <v>49.82215161808719</v>
+        <v>49.36156033646038</v>
       </c>
       <c r="D18">
-        <v>54.08615161808719</v>
+        <v>54.22956033646038</v>
       </c>
       <c r="E18">
-        <v>-8.635999999999999</v>
+        <v>-8.031999999999998</v>
       </c>
       <c r="F18">
-        <v>9.664000000000001</v>
+        <v>10.268</v>
       </c>
       <c r="G18">
         <v>5.4</v>
@@ -2763,28 +2763,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M18">
-        <v>0.5344192000000001</v>
+        <v>0.5678204000000001</v>
       </c>
       <c r="N18">
-        <v>2.479662432653061</v>
+        <v>2.446261232653062</v>
       </c>
       <c r="O18">
-        <v>0.4959324865306123</v>
+        <v>0.4892522465306123</v>
       </c>
       <c r="P18">
-        <v>1.983729946122449</v>
+        <v>1.957008986122449</v>
       </c>
       <c r="Q18">
-        <v>6.173729946122449</v>
+        <v>6.147008986122449</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07926918500145078</v>
+        <v>0.07960244383846612</v>
       </c>
       <c r="T18">
-        <v>0.6523767118395591</v>
+        <v>0.6588725468673353</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.639920183730414</v>
+        <v>5.308160172922743</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07359082838592687</v>
+        <v>0.07351714137063511</v>
       </c>
       <c r="C19">
-        <v>49.36156033646038</v>
+        <v>48.90173156928497</v>
       </c>
       <c r="D19">
-        <v>54.22956033646038</v>
+        <v>54.37373156928497</v>
       </c>
       <c r="E19">
-        <v>-8.031999999999998</v>
+        <v>-7.427999999999999</v>
       </c>
       <c r="F19">
-        <v>10.268</v>
+        <v>10.872</v>
       </c>
       <c r="G19">
         <v>5.4</v>
@@ -2845,28 +2845,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M19">
-        <v>0.5678204000000001</v>
+        <v>0.6012216000000001</v>
       </c>
       <c r="N19">
-        <v>2.446261232653062</v>
+        <v>2.412860032653061</v>
       </c>
       <c r="O19">
-        <v>0.4892522465306123</v>
+        <v>0.4825720065306123</v>
       </c>
       <c r="P19">
-        <v>1.957008986122449</v>
+        <v>1.930288026122449</v>
       </c>
       <c r="Q19">
-        <v>6.147008986122449</v>
+        <v>6.120288026122449</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07960244383846612</v>
+        <v>0.07994383093979891</v>
       </c>
       <c r="T19">
-        <v>0.6588725468673353</v>
+        <v>0.665526816895789</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.308160172922743</v>
+        <v>5.013262385538146</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07351714137063511</v>
+        <v>0.07344345435534334</v>
       </c>
       <c r="C20">
-        <v>48.90173156928497</v>
+        <v>48.44267141428817</v>
       </c>
       <c r="D20">
-        <v>54.37373156928497</v>
+        <v>54.51867141428817</v>
       </c>
       <c r="E20">
-        <v>-7.428000000000001</v>
+        <v>-6.824</v>
       </c>
       <c r="F20">
-        <v>10.872</v>
+        <v>11.476</v>
       </c>
       <c r="G20">
         <v>5.4</v>
@@ -2927,28 +2927,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M20">
-        <v>0.6012216</v>
+        <v>0.6346228</v>
       </c>
       <c r="N20">
-        <v>2.412860032653061</v>
+        <v>2.379458832653062</v>
       </c>
       <c r="O20">
-        <v>0.4825720065306123</v>
+        <v>0.4758917665306124</v>
       </c>
       <c r="P20">
-        <v>1.930288026122449</v>
+        <v>1.903567066122449</v>
       </c>
       <c r="Q20">
-        <v>6.120288026122449</v>
+        <v>6.093567066122449</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07994383093979891</v>
+        <v>0.08029364735227573</v>
       </c>
       <c r="T20">
-        <v>0.6655268168957889</v>
+        <v>0.6723453898879082</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.013262385538146</v>
+        <v>4.749406470509824</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07344345435534334</v>
+        <v>0.07336976734005156</v>
       </c>
       <c r="C21">
-        <v>48.44267141428817</v>
+        <v>47.98438603438785</v>
       </c>
       <c r="D21">
-        <v>54.51867141428817</v>
+        <v>54.66438603438786</v>
       </c>
       <c r="E21">
-        <v>-6.824</v>
+        <v>-6.219999999999999</v>
       </c>
       <c r="F21">
-        <v>11.476</v>
+        <v>12.08</v>
       </c>
       <c r="G21">
         <v>5.4</v>
@@ -3009,28 +3009,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M21">
-        <v>0.6346228</v>
+        <v>0.6680240000000002</v>
       </c>
       <c r="N21">
-        <v>2.379458832653062</v>
+        <v>2.346057632653062</v>
       </c>
       <c r="O21">
-        <v>0.4758917665306124</v>
+        <v>0.4692115265306123</v>
       </c>
       <c r="P21">
-        <v>1.903567066122449</v>
+        <v>1.876846106122449</v>
       </c>
       <c r="Q21">
-        <v>6.093567066122449</v>
+        <v>6.066846106122449</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08029364735227573</v>
+        <v>0.08065220917506445</v>
       </c>
       <c r="T21">
-        <v>0.6723453898879082</v>
+        <v>0.6793344272048302</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.749406470509824</v>
+        <v>4.511936146984331</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07336976734005156</v>
+        <v>0.07371608032475979</v>
       </c>
       <c r="C22">
-        <v>47.98438603438785</v>
+        <v>46.702246895061</v>
       </c>
       <c r="D22">
-        <v>54.66438603438786</v>
+        <v>53.98624689506101</v>
       </c>
       <c r="E22">
-        <v>-6.219999999999999</v>
+        <v>-5.615999999999998</v>
       </c>
       <c r="F22">
-        <v>12.08</v>
+        <v>12.684</v>
       </c>
       <c r="G22">
         <v>5.4</v>
@@ -3091,45 +3091,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M22">
-        <v>0.6680240000000002</v>
+        <v>0.7331352000000002</v>
       </c>
       <c r="N22">
-        <v>2.346057632653062</v>
+        <v>2.280946432653061</v>
       </c>
       <c r="O22">
-        <v>0.4692115265306123</v>
+        <v>0.4561892865306122</v>
       </c>
       <c r="P22">
-        <v>1.876846106122449</v>
+        <v>1.824757146122449</v>
       </c>
       <c r="Q22">
-        <v>6.066846106122449</v>
+        <v>6.014757146122449</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08065220917506445</v>
+        <v>0.08101984851235416</v>
       </c>
       <c r="T22">
-        <v>0.6793344272048302</v>
+        <v>0.6865004021753452</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.511936146984331</v>
+        <v>4.111222094714673</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07371608032475979</v>
+        <v>0.07427839330946802</v>
       </c>
       <c r="C23">
-        <v>46.70224689506101</v>
+        <v>45.03227497400237</v>
       </c>
       <c r="D23">
-        <v>53.98624689506101</v>
+        <v>52.92027497400237</v>
       </c>
       <c r="E23">
-        <v>-5.616</v>
+        <v>-5.011999999999999</v>
       </c>
       <c r="F23">
-        <v>12.684</v>
+        <v>13.288</v>
       </c>
       <c r="G23">
         <v>5.4</v>
@@ -3173,45 +3173,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M23">
-        <v>0.7331352000000001</v>
+        <v>0.8145544000000001</v>
       </c>
       <c r="N23">
-        <v>2.280946432653062</v>
+        <v>2.199527232653061</v>
       </c>
       <c r="O23">
-        <v>0.4561892865306123</v>
+        <v>0.4399054465306123</v>
       </c>
       <c r="P23">
-        <v>1.824757146122449</v>
+        <v>1.759621786122449</v>
       </c>
       <c r="Q23">
-        <v>6.014757146122449</v>
+        <v>5.949621786122449</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08101984851235416</v>
+        <v>0.08139691449931796</v>
       </c>
       <c r="T23">
-        <v>0.6865004021753452</v>
+        <v>0.6938501200938223</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.111222094714673</v>
+        <v>3.70028279591033</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07427839330946802</v>
+        <v>0.07425270629417624</v>
       </c>
       <c r="C24">
-        <v>45.03227497400237</v>
+        <v>44.47605123466621</v>
       </c>
       <c r="D24">
-        <v>52.92027497400237</v>
+        <v>52.96805123466621</v>
       </c>
       <c r="E24">
-        <v>-5.011999999999999</v>
+        <v>-4.407999999999999</v>
       </c>
       <c r="F24">
-        <v>13.288</v>
+        <v>13.892</v>
       </c>
       <c r="G24">
         <v>5.4</v>
@@ -3255,28 +3255,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M24">
-        <v>0.8145544000000001</v>
+        <v>0.8515796000000001</v>
       </c>
       <c r="N24">
-        <v>2.199527232653061</v>
+        <v>2.162502032653062</v>
       </c>
       <c r="O24">
-        <v>0.4399054465306123</v>
+        <v>0.4325004065306123</v>
       </c>
       <c r="P24">
-        <v>1.759621786122449</v>
+        <v>1.730001626122449</v>
       </c>
       <c r="Q24">
-        <v>5.949621786122449</v>
+        <v>5.920001626122449</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08139691449931796</v>
+        <v>0.08178377440802109</v>
       </c>
       <c r="T24">
-        <v>0.6938501200938223</v>
+        <v>0.7013907397764156</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.70028279591033</v>
+        <v>3.539400935218576</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07425270629417624</v>
+        <v>0.07476461927888446</v>
       </c>
       <c r="C25">
-        <v>44.47605123466621</v>
+        <v>42.93590797172048</v>
       </c>
       <c r="D25">
-        <v>52.96805123466621</v>
+        <v>52.03190797172048</v>
       </c>
       <c r="E25">
-        <v>-4.407999999999999</v>
+        <v>-3.803999999999998</v>
       </c>
       <c r="F25">
-        <v>13.892</v>
+        <v>14.496</v>
       </c>
       <c r="G25">
         <v>5.4</v>
@@ -3337,45 +3337,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M25">
-        <v>0.8515796000000001</v>
+        <v>0.9291936000000002</v>
       </c>
       <c r="N25">
-        <v>2.162502032653062</v>
+        <v>2.084888032653061</v>
       </c>
       <c r="O25">
-        <v>0.4325004065306123</v>
+        <v>0.4169776065306123</v>
       </c>
       <c r="P25">
-        <v>1.730001626122449</v>
+        <v>1.667910426122449</v>
       </c>
       <c r="Q25">
-        <v>5.920001626122449</v>
+        <v>5.857910426122449</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08178377440802109</v>
+        <v>0.08218081484063745</v>
       </c>
       <c r="T25">
-        <v>0.7013907397764156</v>
+        <v>0.7091297968190772</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.539400935218576</v>
+        <v>3.243760646492896</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07476461927888446</v>
+        <v>0.0747613322635927</v>
       </c>
       <c r="C26">
-        <v>42.93590797172048</v>
+        <v>42.33781342094517</v>
       </c>
       <c r="D26">
-        <v>52.03190797172048</v>
+        <v>52.03781342094518</v>
       </c>
       <c r="E26">
-        <v>-3.804</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="F26">
-        <v>14.496</v>
+        <v>15.1</v>
       </c>
       <c r="G26">
         <v>5.4</v>
@@ -3419,28 +3419,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M26">
-        <v>0.9291936000000001</v>
+        <v>0.9679100000000002</v>
       </c>
       <c r="N26">
-        <v>2.084888032653061</v>
+        <v>2.046171632653061</v>
       </c>
       <c r="O26">
-        <v>0.4169776065306123</v>
+        <v>0.4092343265306123</v>
       </c>
       <c r="P26">
-        <v>1.667910426122449</v>
+        <v>1.636937306122449</v>
       </c>
       <c r="Q26">
-        <v>5.857910426122449</v>
+        <v>5.826937306122448</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08218081484063744</v>
+        <v>0.0825884430181236</v>
       </c>
       <c r="T26">
-        <v>0.7091297968190771</v>
+        <v>0.7170752287162097</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.243760646492896</v>
+        <v>3.11401022063318</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0747613322635927</v>
+        <v>0.07638044524830093</v>
       </c>
       <c r="C27">
-        <v>42.33781342094517</v>
+        <v>38.97861810833417</v>
       </c>
       <c r="D27">
-        <v>52.03781342094518</v>
+        <v>49.28261810833417</v>
       </c>
       <c r="E27">
-        <v>-3.199999999999999</v>
+        <v>-2.595999999999998</v>
       </c>
       <c r="F27">
-        <v>15.1</v>
+        <v>15.704</v>
       </c>
       <c r="G27">
         <v>5.4</v>
@@ -3501,45 +3501,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M27">
-        <v>0.9679100000000002</v>
+        <v>1.1291176</v>
       </c>
       <c r="N27">
-        <v>2.046171632653061</v>
+        <v>1.884964032653061</v>
       </c>
       <c r="O27">
-        <v>0.4092343265306123</v>
+        <v>0.3769928065306123</v>
       </c>
       <c r="P27">
-        <v>1.636937306122449</v>
+        <v>1.507971226122449</v>
       </c>
       <c r="Q27">
-        <v>5.826937306122448</v>
+        <v>5.697971226122449</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0825884430181236</v>
+        <v>0.08300708817337962</v>
       </c>
       <c r="T27">
-        <v>0.7170752287162097</v>
+        <v>0.7252354020159674</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.11401022063318</v>
+        <v>2.669413383205665</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07638044524830093</v>
+        <v>0.07643955823300914</v>
       </c>
       <c r="C28">
-        <v>38.97861810833417</v>
+        <v>38.27953701648343</v>
       </c>
       <c r="D28">
-        <v>49.28261810833417</v>
+        <v>49.18753701648343</v>
       </c>
       <c r="E28">
-        <v>-2.595999999999998</v>
+        <v>-1.991999999999997</v>
       </c>
       <c r="F28">
-        <v>15.704</v>
+        <v>16.308</v>
       </c>
       <c r="G28">
         <v>5.4</v>
@@ -3583,28 +3583,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M28">
-        <v>1.1291176</v>
+        <v>1.1725452</v>
       </c>
       <c r="N28">
-        <v>1.884964032653061</v>
+        <v>1.841536432653061</v>
       </c>
       <c r="O28">
-        <v>0.3769928065306123</v>
+        <v>0.3683072865306123</v>
       </c>
       <c r="P28">
-        <v>1.507971226122449</v>
+        <v>1.473229146122449</v>
       </c>
       <c r="Q28">
-        <v>5.697971226122449</v>
+        <v>5.663229146122449</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08300708817337962</v>
+        <v>0.08343720305891664</v>
       </c>
       <c r="T28">
-        <v>0.7252354020159674</v>
+        <v>0.7336191417074993</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.669413383205665</v>
+        <v>2.570546220864714</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07643955823300914</v>
+        <v>0.07737227121771736</v>
       </c>
       <c r="C29">
-        <v>38.27953701648343</v>
+        <v>36.22243108866708</v>
       </c>
       <c r="D29">
-        <v>49.18753701648343</v>
+        <v>47.73443108866709</v>
       </c>
       <c r="E29">
-        <v>-1.991999999999997</v>
+        <v>-1.387999999999998</v>
       </c>
       <c r="F29">
-        <v>16.308</v>
+        <v>16.912</v>
       </c>
       <c r="G29">
         <v>5.4</v>
@@ -3665,45 +3665,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M29">
-        <v>1.1725452</v>
+        <v>1.2819296</v>
       </c>
       <c r="N29">
-        <v>1.841536432653061</v>
+        <v>1.732152032653061</v>
       </c>
       <c r="O29">
-        <v>0.3683072865306123</v>
+        <v>0.3464304065306123</v>
       </c>
       <c r="P29">
-        <v>1.473229146122449</v>
+        <v>1.385721626122449</v>
       </c>
       <c r="Q29">
-        <v>5.663229146122449</v>
+        <v>5.575721626122449</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08343720305891664</v>
+        <v>0.08387926558016301</v>
       </c>
       <c r="T29">
-        <v>0.7336191417074993</v>
+        <v>0.7422357630571292</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.570546220864714</v>
+        <v>2.351206831212151</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07737227121771736</v>
+        <v>0.07746258420242559</v>
       </c>
       <c r="C30">
-        <v>36.22243108866708</v>
+        <v>35.48227546354801</v>
       </c>
       <c r="D30">
-        <v>47.73443108866709</v>
+        <v>47.59827546354801</v>
       </c>
       <c r="E30">
-        <v>-1.387999999999998</v>
+        <v>-0.7839999999999954</v>
       </c>
       <c r="F30">
-        <v>16.912</v>
+        <v>17.51600000000001</v>
       </c>
       <c r="G30">
         <v>5.4</v>
@@ -3747,28 +3747,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M30">
-        <v>1.2819296</v>
+        <v>1.3277128</v>
       </c>
       <c r="N30">
-        <v>1.732152032653061</v>
+        <v>1.686368832653061</v>
       </c>
       <c r="O30">
-        <v>0.3464304065306123</v>
+        <v>0.3372737665306123</v>
       </c>
       <c r="P30">
-        <v>1.385721626122449</v>
+        <v>1.349095066122449</v>
       </c>
       <c r="Q30">
-        <v>5.575721626122449</v>
+        <v>5.539095066122449</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08387926558016301</v>
+        <v>0.08433378056679661</v>
       </c>
       <c r="T30">
-        <v>0.7422357630571292</v>
+        <v>0.7510951061349179</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.351206831212151</v>
+        <v>2.270130733584146</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07746258420242558</v>
+        <v>0.07755289718713382</v>
       </c>
       <c r="C31">
-        <v>35.48227546354804</v>
+        <v>34.74289435804627</v>
       </c>
       <c r="D31">
-        <v>47.59827546354803</v>
+        <v>47.46289435804627</v>
       </c>
       <c r="E31">
-        <v>-0.7839999999999989</v>
+        <v>-0.1799999999999997</v>
       </c>
       <c r="F31">
-        <v>17.516</v>
+        <v>18.12</v>
       </c>
       <c r="G31">
         <v>5.4</v>
@@ -3829,28 +3829,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M31">
-        <v>1.3277128</v>
+        <v>1.373496</v>
       </c>
       <c r="N31">
-        <v>1.686368832653061</v>
+        <v>1.640585632653061</v>
       </c>
       <c r="O31">
-        <v>0.3372737665306123</v>
+        <v>0.3281171265306123</v>
       </c>
       <c r="P31">
-        <v>1.349095066122449</v>
+        <v>1.312468506122449</v>
       </c>
       <c r="Q31">
-        <v>5.539095066122449</v>
+        <v>5.502468506122448</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08433378056679661</v>
+        <v>0.08480128169590545</v>
       </c>
       <c r="T31">
-        <v>0.7510951061349179</v>
+        <v>0.7602075733006434</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.270130733584146</v>
+        <v>2.194459709131341</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07755289718713382</v>
+        <v>0.07764321017184204</v>
       </c>
       <c r="C32">
-        <v>34.74289435804627</v>
+        <v>34.00428118213736</v>
       </c>
       <c r="D32">
-        <v>47.46289435804627</v>
+        <v>47.32828118213737</v>
       </c>
       <c r="E32">
-        <v>-0.1799999999999997</v>
+        <v>0.4239999999999995</v>
       </c>
       <c r="F32">
-        <v>18.12</v>
+        <v>18.724</v>
       </c>
       <c r="G32">
         <v>5.4</v>
@@ -3911,28 +3911,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M32">
-        <v>1.373496</v>
+        <v>1.4192792</v>
       </c>
       <c r="N32">
-        <v>1.640585632653061</v>
+        <v>1.594802432653061</v>
       </c>
       <c r="O32">
-        <v>0.3281171265306123</v>
+        <v>0.3189604865306123</v>
       </c>
       <c r="P32">
-        <v>1.312468506122449</v>
+        <v>1.275841946122449</v>
       </c>
       <c r="Q32">
-        <v>5.502468506122448</v>
+        <v>5.465841946122449</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08480128169590545</v>
+        <v>0.08528233358237977</v>
       </c>
       <c r="T32">
-        <v>0.7602075733006434</v>
+        <v>0.7695841699494332</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.194459709131341</v>
+        <v>2.123670686256137</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07764321017184204</v>
+        <v>0.07773352315655027</v>
       </c>
       <c r="C33">
-        <v>34.00428118213736</v>
+        <v>33.26642942034727</v>
       </c>
       <c r="D33">
-        <v>47.32828118213737</v>
+        <v>47.19442942034727</v>
       </c>
       <c r="E33">
-        <v>0.4239999999999995</v>
+        <v>1.028000000000002</v>
       </c>
       <c r="F33">
-        <v>18.724</v>
+        <v>19.328</v>
       </c>
       <c r="G33">
         <v>5.4</v>
@@ -3993,28 +3993,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M33">
-        <v>1.4192792</v>
+        <v>1.4650624</v>
       </c>
       <c r="N33">
-        <v>1.594802432653061</v>
+        <v>1.549019232653061</v>
       </c>
       <c r="O33">
-        <v>0.3189604865306123</v>
+        <v>0.3098038465306123</v>
       </c>
       <c r="P33">
-        <v>1.275841946122449</v>
+        <v>1.239215386122449</v>
       </c>
       <c r="Q33">
-        <v>5.465841946122449</v>
+        <v>5.429215386122449</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08528233358237977</v>
+        <v>0.0857775340537504</v>
       </c>
       <c r="T33">
-        <v>0.7695841699494332</v>
+        <v>0.7792365488525993</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.123670686256137</v>
+        <v>2.057305977310633</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07773352315655027</v>
+        <v>0.08157263614125849</v>
       </c>
       <c r="C34">
-        <v>33.26642942034727</v>
+        <v>27.59753160073758</v>
       </c>
       <c r="D34">
-        <v>47.19442942034727</v>
+        <v>42.12953160073758</v>
       </c>
       <c r="E34">
-        <v>1.028000000000002</v>
+        <v>1.632000000000001</v>
       </c>
       <c r="F34">
-        <v>19.328</v>
+        <v>19.932</v>
       </c>
       <c r="G34">
         <v>5.4</v>
@@ -4075,45 +4075,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M34">
-        <v>1.4650624</v>
+        <v>1.79388</v>
       </c>
       <c r="N34">
-        <v>1.549019232653061</v>
+        <v>1.220201632653061</v>
       </c>
       <c r="O34">
-        <v>0.3098038465306123</v>
+        <v>0.2440403265306123</v>
       </c>
       <c r="P34">
-        <v>1.239215386122449</v>
+        <v>0.9761613061224491</v>
       </c>
       <c r="Q34">
-        <v>5.429215386122449</v>
+        <v>5.166161306122449</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0857775340537504</v>
+        <v>0.08628751662874404</v>
       </c>
       <c r="T34">
-        <v>0.7792365488525993</v>
+        <v>0.7891770584692929</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.057305977310633</v>
+        <v>1.680202484365209</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08157263614125849</v>
+        <v>0.08177654912596671</v>
       </c>
       <c r="C35">
-        <v>27.59753160073758</v>
+        <v>26.75474386979133</v>
       </c>
       <c r="D35">
-        <v>42.12953160073758</v>
+        <v>41.89074386979134</v>
       </c>
       <c r="E35">
-        <v>1.632000000000001</v>
+        <v>2.236000000000004</v>
       </c>
       <c r="F35">
-        <v>19.932</v>
+        <v>20.536</v>
       </c>
       <c r="G35">
         <v>5.4</v>
@@ -4157,28 +4157,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M35">
-        <v>1.79388</v>
+        <v>1.84824</v>
       </c>
       <c r="N35">
-        <v>1.220201632653061</v>
+        <v>1.165841632653061</v>
       </c>
       <c r="O35">
-        <v>0.2440403265306123</v>
+        <v>0.2331683265306123</v>
       </c>
       <c r="P35">
-        <v>0.9761613061224491</v>
+        <v>0.9326733061224489</v>
       </c>
       <c r="Q35">
-        <v>5.166161306122449</v>
+        <v>5.122673306122448</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08628751662874404</v>
+        <v>0.0868129532211617</v>
       </c>
       <c r="T35">
-        <v>0.7891770584692929</v>
+        <v>0.7994187956501284</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.680202484365209</v>
+        <v>1.63078476423682</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08177654912596671</v>
+        <v>0.08198046211067495</v>
       </c>
       <c r="C36">
-        <v>26.75474386979133</v>
+        <v>25.91464775283165</v>
       </c>
       <c r="D36">
-        <v>41.89074386979134</v>
+        <v>41.65464775283166</v>
       </c>
       <c r="E36">
-        <v>2.236000000000004</v>
+        <v>2.840000000000003</v>
       </c>
       <c r="F36">
-        <v>20.536</v>
+        <v>21.14</v>
       </c>
       <c r="G36">
         <v>5.4</v>
@@ -4239,28 +4239,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M36">
-        <v>1.84824</v>
+        <v>1.9026</v>
       </c>
       <c r="N36">
-        <v>1.165841632653061</v>
+        <v>1.111481632653061</v>
       </c>
       <c r="O36">
-        <v>0.2331683265306123</v>
+        <v>0.2222963265306123</v>
       </c>
       <c r="P36">
-        <v>0.9326733061224489</v>
+        <v>0.8891853061224489</v>
       </c>
       <c r="Q36">
-        <v>5.122673306122448</v>
+        <v>5.079185306122448</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0868129532211617</v>
+        <v>0.08735455709334608</v>
       </c>
       <c r="T36">
-        <v>0.7994187956501284</v>
+        <v>0.8099756632057591</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.63078476423682</v>
+        <v>1.584190913830054</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08198046211067495</v>
+        <v>0.08218437509538318</v>
       </c>
       <c r="C37">
-        <v>25.91464775283165</v>
+        <v>25.07719799512707</v>
       </c>
       <c r="D37">
-        <v>41.65464775283166</v>
+        <v>41.42119799512707</v>
       </c>
       <c r="E37">
-        <v>2.840000000000003</v>
+        <v>3.444000000000003</v>
       </c>
       <c r="F37">
-        <v>21.14</v>
+        <v>21.744</v>
       </c>
       <c r="G37">
         <v>5.4</v>
@@ -4321,28 +4321,28 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M37">
-        <v>1.9026</v>
+        <v>1.95696</v>
       </c>
       <c r="N37">
-        <v>1.111481632653061</v>
+        <v>1.057121632653061</v>
       </c>
       <c r="O37">
-        <v>0.2222963265306123</v>
+        <v>0.2114243265306123</v>
       </c>
       <c r="P37">
-        <v>0.8891853061224489</v>
+        <v>0.845697306122449</v>
       </c>
       <c r="Q37">
-        <v>5.079185306122448</v>
+        <v>5.035697306122448</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08735455709334608</v>
+        <v>0.08791308608653622</v>
       </c>
       <c r="T37">
-        <v>0.8099756632057591</v>
+        <v>0.8208624328725033</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.584190913830054</v>
+        <v>1.540185610668108</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08218437509538318</v>
+        <v>0.1002585415114708</v>
       </c>
       <c r="C38">
-        <v>25.07719799512707</v>
+        <v>10.7259766238028</v>
       </c>
       <c r="D38">
-        <v>41.42119799512707</v>
+        <v>27.6739766238028</v>
       </c>
       <c r="E38">
-        <v>3.443999999999999</v>
+        <v>4.048000000000002</v>
       </c>
       <c r="F38">
-        <v>21.744</v>
+        <v>22.348</v>
       </c>
       <c r="G38">
         <v>5.4</v>
@@ -4403,45 +4403,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M38">
-        <v>1.95696</v>
+        <v>3.280686400000001</v>
       </c>
       <c r="N38">
-        <v>1.057121632653062</v>
+        <v>-0.2666047673469394</v>
       </c>
       <c r="O38">
-        <v>0.2114243265306124</v>
+        <v>-0.05332095346938788</v>
       </c>
       <c r="P38">
-        <v>0.8456973061224493</v>
+        <v>-0.2132838138775515</v>
       </c>
       <c r="Q38">
-        <v>5.035697306122449</v>
+        <v>3.976716186122448</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08791308608653621</v>
+        <v>0.0887665782041272</v>
       </c>
       <c r="T38">
-        <v>0.8208624328725032</v>
+        <v>0.8374985828483946</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2</v>
+        <v>0.1837470129819821</v>
       </c>
       <c r="W38">
-        <v>0.07199999999999999</v>
+        <v>0.119825938494245</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.540185610668109</v>
+        <v>0.9187350649099105</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1002585415114708</v>
+        <v>0.1012685415114708</v>
       </c>
       <c r="C39">
-        <v>10.7259766238028</v>
+        <v>9.618074490658355</v>
       </c>
       <c r="D39">
-        <v>27.6739766238028</v>
+        <v>27.17007449065836</v>
       </c>
       <c r="E39">
-        <v>4.048000000000002</v>
+        <v>4.652000000000001</v>
       </c>
       <c r="F39">
-        <v>22.348</v>
+        <v>22.952</v>
       </c>
       <c r="G39">
         <v>5.4</v>
@@ -4485,37 +4485,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M39">
-        <v>3.280686400000001</v>
+        <v>3.369353600000001</v>
       </c>
       <c r="N39">
-        <v>-0.2666047673469394</v>
+        <v>-0.3552719673469391</v>
       </c>
       <c r="O39">
-        <v>-0.05332095346938788</v>
+        <v>-0.07105439346938783</v>
       </c>
       <c r="P39">
-        <v>-0.2132838138775515</v>
+        <v>-0.2842175738775513</v>
       </c>
       <c r="Q39">
-        <v>3.976716186122448</v>
+        <v>3.905782426122448</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0887665782041272</v>
+        <v>0.08945958753000022</v>
       </c>
       <c r="T39">
-        <v>0.8374985828483946</v>
+        <v>0.8510066245072397</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1837470129819821</v>
+        <v>0.17891156527193</v>
       </c>
       <c r="W39">
-        <v>0.119825938494245</v>
+        <v>0.1205357822180807</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9187350649099105</v>
+        <v>0.8945578263596498</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1012685415114708</v>
+        <v>0.1022785415114708</v>
       </c>
       <c r="C40">
-        <v>9.618074490658355</v>
+        <v>8.528194818464783</v>
       </c>
       <c r="D40">
-        <v>27.17007449065836</v>
+        <v>26.68419481846479</v>
       </c>
       <c r="E40">
-        <v>4.652000000000001</v>
+        <v>5.256000000000004</v>
       </c>
       <c r="F40">
-        <v>22.952</v>
+        <v>23.556</v>
       </c>
       <c r="G40">
         <v>5.4</v>
@@ -4567,37 +4567,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M40">
-        <v>3.369353600000001</v>
+        <v>3.458020800000001</v>
       </c>
       <c r="N40">
-        <v>-0.3552719673469391</v>
+        <v>-0.4439391673469393</v>
       </c>
       <c r="O40">
-        <v>-0.07105439346938783</v>
+        <v>-0.08878783346938786</v>
       </c>
       <c r="P40">
-        <v>-0.2842175738775513</v>
+        <v>-0.3551513338775514</v>
       </c>
       <c r="Q40">
-        <v>3.905782426122448</v>
+        <v>3.834848666122448</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08945958753000022</v>
+        <v>0.09017531847311497</v>
       </c>
       <c r="T40">
-        <v>0.8510066245072397</v>
+        <v>0.86495755277785</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.17891156527193</v>
+        <v>0.1743240892393164</v>
       </c>
       <c r="W40">
-        <v>0.1205357822180807</v>
+        <v>0.1212092236996684</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8945578263596498</v>
+        <v>0.8716204461965819</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1022785415114708</v>
+        <v>0.1032885415114708</v>
       </c>
       <c r="C41">
-        <v>8.528194818464783</v>
+        <v>7.455387712595311</v>
       </c>
       <c r="D41">
-        <v>26.68419481846479</v>
+        <v>26.21538771259531</v>
       </c>
       <c r="E41">
-        <v>5.256000000000004</v>
+        <v>5.860000000000003</v>
       </c>
       <c r="F41">
-        <v>23.556</v>
+        <v>24.16</v>
       </c>
       <c r="G41">
         <v>5.4</v>
@@ -4649,37 +4649,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M41">
-        <v>3.458020800000001</v>
+        <v>3.546688000000001</v>
       </c>
       <c r="N41">
-        <v>-0.4439391673469393</v>
+        <v>-0.5326063673469394</v>
       </c>
       <c r="O41">
-        <v>-0.08878783346938786</v>
+        <v>-0.1065212734693879</v>
       </c>
       <c r="P41">
-        <v>-0.3551513338775514</v>
+        <v>-0.4260850938775516</v>
       </c>
       <c r="Q41">
-        <v>3.834848666122448</v>
+        <v>3.763914906122448</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09017531847311497</v>
+        <v>0.09091490711433356</v>
       </c>
       <c r="T41">
-        <v>0.86495755277785</v>
+        <v>0.8793735119908143</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1743240892393164</v>
+        <v>0.1699659870083335</v>
       </c>
       <c r="W41">
-        <v>0.1212092236996684</v>
+        <v>0.1218489931071767</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8716204461965819</v>
+        <v>0.8498299350416673</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1032885415114708</v>
+        <v>0.1042985415114708</v>
       </c>
       <c r="C42">
-        <v>7.455387712595311</v>
+        <v>6.398768879619283</v>
       </c>
       <c r="D42">
-        <v>26.21538771259531</v>
+        <v>25.76276887961929</v>
       </c>
       <c r="E42">
-        <v>5.860000000000003</v>
+        <v>6.464000000000002</v>
       </c>
       <c r="F42">
-        <v>24.16</v>
+        <v>24.764</v>
       </c>
       <c r="G42">
         <v>5.4</v>
@@ -4731,37 +4731,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M42">
-        <v>3.546688000000001</v>
+        <v>3.635355200000001</v>
       </c>
       <c r="N42">
-        <v>-0.5326063673469394</v>
+        <v>-0.6212735673469392</v>
       </c>
       <c r="O42">
-        <v>-0.1065212734693879</v>
+        <v>-0.1242547134693878</v>
       </c>
       <c r="P42">
-        <v>-0.4260850938775516</v>
+        <v>-0.4970188538775513</v>
       </c>
       <c r="Q42">
-        <v>3.763914906122448</v>
+        <v>3.692981146122448</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09091490711433356</v>
+        <v>0.09167956655694938</v>
       </c>
       <c r="T42">
-        <v>0.8793735119908143</v>
+        <v>0.8942781477872688</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1699659870083335</v>
+        <v>0.1658204751300814</v>
       </c>
       <c r="W42">
-        <v>0.1218489931071767</v>
+        <v>0.1224575542509041</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8498299350416673</v>
+        <v>0.8291023756504071</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1042985415114708</v>
+        <v>0.1053085415114708</v>
       </c>
       <c r="C43">
-        <v>6.398768879619283</v>
+        <v>5.357514060268681</v>
       </c>
       <c r="D43">
-        <v>25.76276887961929</v>
+        <v>25.32551406026868</v>
       </c>
       <c r="E43">
-        <v>6.464000000000002</v>
+        <v>7.068000000000005</v>
       </c>
       <c r="F43">
-        <v>24.764</v>
+        <v>25.36800000000001</v>
       </c>
       <c r="G43">
         <v>5.4</v>
@@ -4813,37 +4813,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M43">
-        <v>3.635355200000001</v>
+        <v>3.724022400000001</v>
       </c>
       <c r="N43">
-        <v>-0.6212735673469392</v>
+        <v>-0.7099407673469398</v>
       </c>
       <c r="O43">
-        <v>-0.1242547134693878</v>
+        <v>-0.141988153469388</v>
       </c>
       <c r="P43">
-        <v>-0.4970188538775513</v>
+        <v>-0.5679526138775518</v>
       </c>
       <c r="Q43">
-        <v>3.692981146122448</v>
+        <v>3.622047386122448</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09167956655694938</v>
+        <v>0.09247059356655196</v>
       </c>
       <c r="T43">
-        <v>0.8942781477872688</v>
+        <v>0.9096967365422217</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1658204751300814</v>
+        <v>0.1618723685793652</v>
       </c>
       <c r="W43">
-        <v>0.1224575542509041</v>
+        <v>0.1230371362925492</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8291023756504071</v>
+        <v>0.8093618428968259</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1053085415114708</v>
+        <v>0.1300695495910201</v>
       </c>
       <c r="C44">
-        <v>5.357514060268691</v>
+        <v>-2.68790767876331</v>
       </c>
       <c r="D44">
-        <v>25.32551406026869</v>
+        <v>17.88409232123669</v>
       </c>
       <c r="E44">
-        <v>7.068000000000001</v>
+        <v>7.672000000000001</v>
       </c>
       <c r="F44">
-        <v>25.368</v>
+        <v>25.972</v>
       </c>
       <c r="G44">
         <v>5.4</v>
@@ -4895,45 +4895,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M44">
-        <v>3.724022400000001</v>
+        <v>5.215177600000001</v>
       </c>
       <c r="N44">
-        <v>-0.7099407673469393</v>
+        <v>-2.201095967346939</v>
       </c>
       <c r="O44">
-        <v>-0.1419881534693879</v>
+        <v>-0.4402191934693878</v>
       </c>
       <c r="P44">
-        <v>-0.5679526138775515</v>
+        <v>-1.760876773877551</v>
       </c>
       <c r="Q44">
-        <v>3.622047386122448</v>
+        <v>2.429123226122448</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09247059356655196</v>
+        <v>0.09422096903184106</v>
       </c>
       <c r="T44">
-        <v>0.9096967365422216</v>
+        <v>0.9438148123328465</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1618723685793652</v>
+        <v>0.1155888394923717</v>
       </c>
       <c r="W44">
-        <v>0.1230371362925492</v>
+        <v>0.1775897610299318</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.809361842896826</v>
+        <v>0.5779441974618584</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1300695495910201</v>
+        <v>0.1316195495910201</v>
       </c>
       <c r="C45">
-        <v>-2.68790767876331</v>
+        <v>-3.614915003201862</v>
       </c>
       <c r="D45">
-        <v>17.88409232123669</v>
+        <v>17.56108499679814</v>
       </c>
       <c r="E45">
-        <v>7.672000000000001</v>
+        <v>8.276000000000003</v>
       </c>
       <c r="F45">
-        <v>25.972</v>
+        <v>26.576</v>
       </c>
       <c r="G45">
         <v>5.4</v>
@@ -4977,37 +4977,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M45">
-        <v>5.215177600000001</v>
+        <v>5.336460800000001</v>
       </c>
       <c r="N45">
-        <v>-2.201095967346939</v>
+        <v>-2.32237916734694</v>
       </c>
       <c r="O45">
-        <v>-0.4402191934693878</v>
+        <v>-0.4644758334693879</v>
       </c>
       <c r="P45">
-        <v>-1.760876773877551</v>
+        <v>-1.857903333877552</v>
       </c>
       <c r="Q45">
-        <v>2.429123226122448</v>
+        <v>2.332096666122448</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09422096903184106</v>
+        <v>0.09508562919312394</v>
       </c>
       <c r="T45">
-        <v>0.9438148123328465</v>
+        <v>0.9606686482673616</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1155888394923717</v>
+        <v>0.1129618204129996</v>
       </c>
       <c r="W45">
-        <v>0.1775897610299318</v>
+        <v>0.1781172664610697</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5779441974618584</v>
+        <v>0.564809102064998</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1316195495910201</v>
+        <v>0.1331695495910201</v>
       </c>
       <c r="C46">
-        <v>-3.614915003201862</v>
+        <v>-4.5304615531435</v>
       </c>
       <c r="D46">
-        <v>17.56108499679814</v>
+        <v>17.2495384468565</v>
       </c>
       <c r="E46">
-        <v>8.276000000000003</v>
+        <v>8.880000000000003</v>
       </c>
       <c r="F46">
-        <v>26.576</v>
+        <v>27.18</v>
       </c>
       <c r="G46">
         <v>5.4</v>
@@ -5059,37 +5059,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M46">
-        <v>5.336460800000001</v>
+        <v>5.457744000000001</v>
       </c>
       <c r="N46">
-        <v>-2.32237916734694</v>
+        <v>-2.443662367346939</v>
       </c>
       <c r="O46">
-        <v>-0.4644758334693879</v>
+        <v>-0.4887324734693879</v>
       </c>
       <c r="P46">
-        <v>-1.857903333877552</v>
+        <v>-1.954929893877551</v>
       </c>
       <c r="Q46">
-        <v>2.332096666122448</v>
+        <v>2.235070106122448</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09508562919312394</v>
+        <v>0.09598173154208982</v>
       </c>
       <c r="T46">
-        <v>0.9606686482673616</v>
+        <v>0.9781353509631318</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1129618204129996</v>
+        <v>0.1104515577371552</v>
       </c>
       <c r="W46">
-        <v>0.1781172664610697</v>
+        <v>0.1786213272063792</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.564809102064998</v>
+        <v>0.5522577886857758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1331695495910201</v>
+        <v>0.1347195495910201</v>
       </c>
       <c r="C47">
-        <v>-4.5304615531435</v>
+        <v>-5.435146663623723</v>
       </c>
       <c r="D47">
-        <v>17.2495384468565</v>
+        <v>16.94885333637628</v>
       </c>
       <c r="E47">
-        <v>8.880000000000003</v>
+        <v>9.484000000000002</v>
       </c>
       <c r="F47">
-        <v>27.18</v>
+        <v>27.784</v>
       </c>
       <c r="G47">
         <v>5.4</v>
@@ -5141,37 +5141,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M47">
-        <v>5.457744000000001</v>
+        <v>5.579027200000001</v>
       </c>
       <c r="N47">
-        <v>-2.443662367346939</v>
+        <v>-2.564945567346939</v>
       </c>
       <c r="O47">
-        <v>-0.4887324734693879</v>
+        <v>-0.5129891134693878</v>
       </c>
       <c r="P47">
-        <v>-1.954929893877551</v>
+        <v>-2.051956453877551</v>
       </c>
       <c r="Q47">
-        <v>2.235070106122448</v>
+        <v>2.138043546122448</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09598173154208982</v>
+        <v>0.09691102286694334</v>
       </c>
       <c r="T47">
-        <v>0.9781353509631318</v>
+        <v>0.9962489685735602</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1104515577371552</v>
+        <v>0.1080504369167822</v>
       </c>
       <c r="W47">
-        <v>0.1786213272063792</v>
+        <v>0.1791034722671101</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5522577886857758</v>
+        <v>0.5402521845839112</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1347195495910201</v>
+        <v>0.1362695495910201</v>
       </c>
       <c r="C48">
-        <v>-5.435146663623723</v>
+        <v>-6.329528596441378</v>
       </c>
       <c r="D48">
-        <v>16.94885333637628</v>
+        <v>16.65847140355863</v>
       </c>
       <c r="E48">
-        <v>9.484000000000002</v>
+        <v>10.088</v>
       </c>
       <c r="F48">
-        <v>27.784</v>
+        <v>28.38800000000001</v>
       </c>
       <c r="G48">
         <v>5.4</v>
@@ -5223,37 +5223,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M48">
-        <v>5.579027200000001</v>
+        <v>5.700310400000001</v>
       </c>
       <c r="N48">
-        <v>-2.564945567346939</v>
+        <v>-2.68622876734694</v>
       </c>
       <c r="O48">
-        <v>-0.5129891134693878</v>
+        <v>-0.537245753469388</v>
       </c>
       <c r="P48">
-        <v>-2.051956453877551</v>
+        <v>-2.148983013877552</v>
       </c>
       <c r="Q48">
-        <v>2.138043546122448</v>
+        <v>2.041016986122448</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09691102286694334</v>
+        <v>0.09787538178896113</v>
       </c>
       <c r="T48">
-        <v>0.9962489685735602</v>
+        <v>1.015046118924005</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1080504369167822</v>
+        <v>0.1057514914504677</v>
       </c>
       <c r="W48">
-        <v>0.1791034722671101</v>
+        <v>0.1795651005167461</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5402521845839112</v>
+        <v>0.5287574572523386</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1362695495910201</v>
+        <v>0.1378195495910201</v>
       </c>
       <c r="C49">
-        <v>-6.329528596441378</v>
+        <v>-7.214127999397334</v>
       </c>
       <c r="D49">
-        <v>16.65847140355863</v>
+        <v>16.37787200060267</v>
       </c>
       <c r="E49">
-        <v>10.088</v>
+        <v>10.692</v>
       </c>
       <c r="F49">
-        <v>28.38800000000001</v>
+        <v>28.992</v>
       </c>
       <c r="G49">
         <v>5.4</v>
@@ -5305,37 +5305,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M49">
-        <v>5.700310400000001</v>
+        <v>5.821593600000001</v>
       </c>
       <c r="N49">
-        <v>-2.68622876734694</v>
+        <v>-2.807511967346939</v>
       </c>
       <c r="O49">
-        <v>-0.537245753469388</v>
+        <v>-0.5615023934693879</v>
       </c>
       <c r="P49">
-        <v>-2.148983013877552</v>
+        <v>-2.246009573877552</v>
       </c>
       <c r="Q49">
-        <v>2.041016986122448</v>
+        <v>1.943990426122448</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09787538178896113</v>
+        <v>0.09887683143874886</v>
       </c>
       <c r="T49">
-        <v>1.015046118924005</v>
+        <v>1.03456623659562</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1057514914504677</v>
+        <v>0.103548335378583</v>
       </c>
       <c r="W49">
-        <v>0.1795651005167461</v>
+        <v>0.1800074942559805</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5287574572523386</v>
+        <v>0.5177416768929148</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1378195495910201</v>
+        <v>0.13936954959102</v>
       </c>
       <c r="C50">
-        <v>-7.214127999397324</v>
+        <v>-8.089431021714866</v>
       </c>
       <c r="D50">
-        <v>16.37787200060268</v>
+        <v>16.10656897828514</v>
       </c>
       <c r="E50">
-        <v>10.692</v>
+        <v>11.296</v>
       </c>
       <c r="F50">
-        <v>28.992</v>
+        <v>29.596</v>
       </c>
       <c r="G50">
         <v>5.4</v>
@@ -5387,37 +5387,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M50">
-        <v>5.8215936</v>
+        <v>5.942876800000001</v>
       </c>
       <c r="N50">
-        <v>-2.807511967346938</v>
+        <v>-2.928795167346939</v>
       </c>
       <c r="O50">
-        <v>-0.5615023934693877</v>
+        <v>-0.5857590334693878</v>
       </c>
       <c r="P50">
-        <v>-2.246009573877551</v>
+        <v>-2.343036133877551</v>
       </c>
       <c r="Q50">
-        <v>1.943990426122449</v>
+        <v>1.846963866122448</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09887683143874886</v>
+        <v>0.09991755362382235</v>
       </c>
       <c r="T50">
-        <v>1.03456623659562</v>
+        <v>1.054851849077887</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.103548335378583</v>
+        <v>0.1014351040443262</v>
       </c>
       <c r="W50">
-        <v>0.1800074942559805</v>
+        <v>0.1804318311078993</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5177416768929149</v>
+        <v>0.5071755202216309</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.13936954959102</v>
+        <v>0.1586338177649845</v>
       </c>
       <c r="C51">
-        <v>-8.089431021714866</v>
+        <v>-11.44332702192297</v>
       </c>
       <c r="D51">
-        <v>16.10656897828514</v>
+        <v>13.35667297807703</v>
       </c>
       <c r="E51">
-        <v>11.296</v>
+        <v>11.9</v>
       </c>
       <c r="F51">
-        <v>29.596</v>
+        <v>30.2</v>
       </c>
       <c r="G51">
         <v>5.4</v>
@@ -5469,45 +5469,45 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M51">
-        <v>5.942876800000001</v>
+        <v>7.121160000000001</v>
       </c>
       <c r="N51">
-        <v>-2.928795167346939</v>
+        <v>-4.107078367346939</v>
       </c>
       <c r="O51">
-        <v>-0.5857590334693878</v>
+        <v>-0.8214156734693878</v>
       </c>
       <c r="P51">
-        <v>-2.343036133877551</v>
+        <v>-3.285662693877551</v>
       </c>
       <c r="Q51">
-        <v>1.846963866122448</v>
+        <v>0.9043373061224482</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09991755362382235</v>
+        <v>0.1014284410442277</v>
       </c>
       <c r="T51">
-        <v>1.054851849077887</v>
+        <v>1.084301857114864</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1014351040443262</v>
+        <v>0.08465142287641512</v>
       </c>
       <c r="W51">
-        <v>0.1804318311078993</v>
+        <v>0.2158391944857413</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5071755202216309</v>
+        <v>0.4232571143820756</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1586338177649845</v>
+        <v>0.1605338177649845</v>
       </c>
       <c r="C52">
-        <v>-11.44332702192297</v>
+        <v>-12.26851445517242</v>
       </c>
       <c r="D52">
-        <v>13.35667297807703</v>
+        <v>13.13548554482758</v>
       </c>
       <c r="E52">
-        <v>11.9</v>
+        <v>12.504</v>
       </c>
       <c r="F52">
-        <v>30.2</v>
+        <v>30.804</v>
       </c>
       <c r="G52">
         <v>5.4</v>
@@ -5551,37 +5551,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M52">
-        <v>7.121160000000001</v>
+        <v>7.263583200000001</v>
       </c>
       <c r="N52">
-        <v>-4.107078367346939</v>
+        <v>-4.24950156734694</v>
       </c>
       <c r="O52">
-        <v>-0.8214156734693878</v>
+        <v>-0.849900313469388</v>
       </c>
       <c r="P52">
-        <v>-3.285662693877551</v>
+        <v>-3.399601253877552</v>
       </c>
       <c r="Q52">
-        <v>0.9043373061224482</v>
+        <v>0.790398746122448</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1014284410442277</v>
+        <v>0.1025637153512528</v>
       </c>
       <c r="T52">
-        <v>1.084301857114864</v>
+        <v>1.106430466443739</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08465142287641512</v>
+        <v>0.08299159105530894</v>
       </c>
       <c r="W52">
-        <v>0.2158391944857413</v>
+        <v>0.2162305828291582</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4232571143820756</v>
+        <v>0.4149579552765447</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1605338177649845</v>
+        <v>0.1624338177649845</v>
       </c>
       <c r="C53">
-        <v>-12.26851445517242</v>
+        <v>-13.08649546868482</v>
       </c>
       <c r="D53">
-        <v>13.13548554482758</v>
+        <v>12.92150453131518</v>
       </c>
       <c r="E53">
-        <v>12.504</v>
+        <v>13.108</v>
       </c>
       <c r="F53">
-        <v>30.804</v>
+        <v>31.408</v>
       </c>
       <c r="G53">
         <v>5.4</v>
@@ -5633,37 +5633,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M53">
-        <v>7.263583200000001</v>
+        <v>7.406006400000002</v>
       </c>
       <c r="N53">
-        <v>-4.24950156734694</v>
+        <v>-4.39192476734694</v>
       </c>
       <c r="O53">
-        <v>-0.849900313469388</v>
+        <v>-0.8783849534693881</v>
       </c>
       <c r="P53">
-        <v>-3.399601253877552</v>
+        <v>-3.513539813877552</v>
       </c>
       <c r="Q53">
-        <v>0.790398746122448</v>
+        <v>0.6764601861224473</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1025637153512528</v>
+        <v>0.1037462927544039</v>
       </c>
       <c r="T53">
-        <v>1.106430466443739</v>
+        <v>1.129481101161317</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08299159105530894</v>
+        <v>0.08139559891962991</v>
       </c>
       <c r="W53">
-        <v>0.2162305828291582</v>
+        <v>0.2166069177747513</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4149579552765447</v>
+        <v>0.4069779945981495</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1624338177649845</v>
+        <v>0.1643338177649845</v>
       </c>
       <c r="C54">
-        <v>-13.08649546868482</v>
+        <v>-13.8976166014756</v>
       </c>
       <c r="D54">
-        <v>12.92150453131518</v>
+        <v>12.71438339852441</v>
       </c>
       <c r="E54">
-        <v>13.108</v>
+        <v>13.71200000000001</v>
       </c>
       <c r="F54">
-        <v>31.408</v>
+        <v>32.01200000000001</v>
       </c>
       <c r="G54">
         <v>5.4</v>
@@ -5715,37 +5715,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M54">
-        <v>7.406006400000002</v>
+        <v>7.548429600000002</v>
       </c>
       <c r="N54">
-        <v>-4.39192476734694</v>
+        <v>-4.534347967346941</v>
       </c>
       <c r="O54">
-        <v>-0.8783849534693881</v>
+        <v>-0.9068695934693882</v>
       </c>
       <c r="P54">
-        <v>-3.513539813877552</v>
+        <v>-3.627478373877552</v>
       </c>
       <c r="Q54">
-        <v>0.6764601861224473</v>
+        <v>0.562521626122447</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1037462927544039</v>
+        <v>0.1049791926002422</v>
       </c>
       <c r="T54">
-        <v>1.129481101161317</v>
+        <v>1.153512613951983</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08139559891962991</v>
+        <v>0.0798598329022784</v>
       </c>
       <c r="W54">
-        <v>0.2166069177747513</v>
+        <v>0.2169690514016428</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4069779945981495</v>
+        <v>0.3992991645113919</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1643338177649845</v>
+        <v>0.1662338177649845</v>
       </c>
       <c r="C55">
-        <v>-13.8976166014756</v>
+        <v>-14.70220252414673</v>
       </c>
       <c r="D55">
-        <v>12.71438339852441</v>
+        <v>12.51379747585328</v>
       </c>
       <c r="E55">
-        <v>13.71200000000001</v>
+        <v>14.31600000000001</v>
       </c>
       <c r="F55">
-        <v>32.01200000000001</v>
+        <v>32.61600000000001</v>
       </c>
       <c r="G55">
         <v>5.4</v>
@@ -5797,37 +5797,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M55">
-        <v>7.548429600000002</v>
+        <v>7.690852800000002</v>
       </c>
       <c r="N55">
-        <v>-4.534347967346941</v>
+        <v>-4.67677116734694</v>
       </c>
       <c r="O55">
-        <v>-0.9068695934693882</v>
+        <v>-0.9353542334693881</v>
       </c>
       <c r="P55">
-        <v>-3.627478373877552</v>
+        <v>-3.741416933877552</v>
       </c>
       <c r="Q55">
-        <v>0.562521626122447</v>
+        <v>0.4485830661224472</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1049791926002422</v>
+        <v>0.106265696787204</v>
       </c>
       <c r="T55">
-        <v>1.153512613951983</v>
+        <v>1.178588975124852</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0798598329022784</v>
+        <v>0.07838094710779177</v>
       </c>
       <c r="W55">
-        <v>0.2169690514016428</v>
+        <v>0.2173177726719827</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3992991645113919</v>
+        <v>0.3919047355389588</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1662338177649845</v>
+        <v>0.1681338177649845</v>
       </c>
       <c r="C56">
-        <v>-14.70220252414673</v>
+        <v>-15.50055773710835</v>
       </c>
       <c r="D56">
-        <v>12.51379747585328</v>
+        <v>12.31944226289166</v>
       </c>
       <c r="E56">
-        <v>14.31600000000001</v>
+        <v>14.92000000000001</v>
       </c>
       <c r="F56">
-        <v>32.61600000000001</v>
+        <v>33.22000000000001</v>
       </c>
       <c r="G56">
         <v>5.4</v>
@@ -5879,37 +5879,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M56">
-        <v>7.690852800000002</v>
+        <v>7.833276000000001</v>
       </c>
       <c r="N56">
-        <v>-4.67677116734694</v>
+        <v>-4.81919436734694</v>
       </c>
       <c r="O56">
-        <v>-0.9353542334693881</v>
+        <v>-0.963838873469388</v>
       </c>
       <c r="P56">
-        <v>-3.741416933877552</v>
+        <v>-3.855355493877552</v>
       </c>
       <c r="Q56">
-        <v>0.4485830661224472</v>
+        <v>0.3346445061224474</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.106265696787204</v>
+        <v>0.1076093789380308</v>
       </c>
       <c r="T56">
-        <v>1.178588975124852</v>
+        <v>1.204779841238738</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07838094710779177</v>
+        <v>0.07695583897855919</v>
       </c>
       <c r="W56">
-        <v>0.2173177726719827</v>
+        <v>0.2176538131688558</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3919047355389588</v>
+        <v>0.3847791948927959</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1681338177649845</v>
+        <v>0.1700338177649845</v>
       </c>
       <c r="C57">
-        <v>-15.50055773710835</v>
+        <v>-16.2929681129673</v>
       </c>
       <c r="D57">
-        <v>12.31944226289166</v>
+        <v>12.1310318870327</v>
       </c>
       <c r="E57">
-        <v>14.92000000000001</v>
+        <v>15.524</v>
       </c>
       <c r="F57">
-        <v>33.22000000000001</v>
+        <v>33.82400000000001</v>
       </c>
       <c r="G57">
         <v>5.4</v>
@@ -5961,37 +5961,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M57">
-        <v>7.833276000000001</v>
+        <v>7.975699200000002</v>
       </c>
       <c r="N57">
-        <v>-4.81919436734694</v>
+        <v>-4.96161756734694</v>
       </c>
       <c r="O57">
-        <v>-0.963838873469388</v>
+        <v>-0.9923235134693882</v>
       </c>
       <c r="P57">
-        <v>-3.855355493877552</v>
+        <v>-3.969294053877552</v>
       </c>
       <c r="Q57">
-        <v>0.3346445061224474</v>
+        <v>0.2207059461224472</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1076093789380308</v>
+        <v>0.1090141375502588</v>
       </c>
       <c r="T57">
-        <v>1.204779841238738</v>
+        <v>1.232161201266891</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07695583897855919</v>
+        <v>0.07558162756822778</v>
       </c>
       <c r="W57">
-        <v>0.2176538131688558</v>
+        <v>0.2179778522194119</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3847791948927959</v>
+        <v>0.3779081378411389</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1700338177649845</v>
+        <v>0.1719338177649845</v>
       </c>
       <c r="C58">
-        <v>-16.2929681129673</v>
+        <v>-17.07970229951438</v>
       </c>
       <c r="D58">
-        <v>12.1310318870327</v>
+        <v>11.94829770048562</v>
       </c>
       <c r="E58">
-        <v>15.524</v>
+        <v>16.128</v>
       </c>
       <c r="F58">
-        <v>33.82400000000001</v>
+        <v>34.428</v>
       </c>
       <c r="G58">
         <v>5.4</v>
@@ -6043,37 +6043,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M58">
-        <v>7.975699200000002</v>
+        <v>8.118122400000001</v>
       </c>
       <c r="N58">
-        <v>-4.96161756734694</v>
+        <v>-5.104040767346939</v>
       </c>
       <c r="O58">
-        <v>-0.9923235134693882</v>
+        <v>-1.020808153469388</v>
       </c>
       <c r="P58">
-        <v>-3.969294053877552</v>
+        <v>-4.083232613877551</v>
       </c>
       <c r="Q58">
-        <v>0.2207059461224472</v>
+        <v>0.1067673861224483</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1090141375502588</v>
+        <v>0.1104842337723578</v>
       </c>
       <c r="T58">
-        <v>1.232161201266891</v>
+        <v>1.260816112924261</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07558162756822778</v>
+        <v>0.07425563410211852</v>
       </c>
       <c r="W58">
-        <v>0.2179778522194119</v>
+        <v>0.2182905214787205</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3779081378411389</v>
+        <v>0.3712781705105926</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1719338177649845</v>
+        <v>0.1738338177649845</v>
       </c>
       <c r="C59">
-        <v>-17.07970229951438</v>
+        <v>-17.86101299779095</v>
       </c>
       <c r="D59">
-        <v>11.94829770048562</v>
+        <v>11.77098700220906</v>
       </c>
       <c r="E59">
-        <v>16.128</v>
+        <v>16.73200000000001</v>
       </c>
       <c r="F59">
-        <v>34.428</v>
+        <v>35.03200000000001</v>
       </c>
       <c r="G59">
         <v>5.4</v>
@@ -6125,37 +6125,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M59">
-        <v>8.118122400000001</v>
+        <v>8.260545600000002</v>
       </c>
       <c r="N59">
-        <v>-5.104040767346939</v>
+        <v>-5.246463967346941</v>
       </c>
       <c r="O59">
-        <v>-1.020808153469388</v>
+        <v>-1.049292793469388</v>
       </c>
       <c r="P59">
-        <v>-4.083232613877551</v>
+        <v>-4.197171173877552</v>
       </c>
       <c r="Q59">
-        <v>0.1067673861224483</v>
+        <v>-0.007171173877552839</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1104842337723578</v>
+        <v>0.1120243345764616</v>
       </c>
       <c r="T59">
-        <v>1.260816112924261</v>
+        <v>1.290835544184362</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07425563410211852</v>
+        <v>0.07297536454863371</v>
       </c>
       <c r="W59">
-        <v>0.2182905214787205</v>
+        <v>0.2185924090394322</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3712781705105926</v>
+        <v>0.3648768227431686</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1738338177649845</v>
+        <v>0.1757338177649845</v>
       </c>
       <c r="C60">
-        <v>-17.86101299779094</v>
+        <v>-18.63713812802185</v>
       </c>
       <c r="D60">
-        <v>11.77098700220906</v>
+        <v>11.59886187197815</v>
       </c>
       <c r="E60">
-        <v>16.732</v>
+        <v>17.336</v>
       </c>
       <c r="F60">
-        <v>35.032</v>
+        <v>35.636</v>
       </c>
       <c r="G60">
         <v>5.4</v>
@@ -6207,37 +6207,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M60">
-        <v>8.2605456</v>
+        <v>8.402968800000002</v>
       </c>
       <c r="N60">
-        <v>-5.246463967346939</v>
+        <v>-5.38888716734694</v>
       </c>
       <c r="O60">
-        <v>-1.049292793469388</v>
+        <v>-1.077777433469388</v>
       </c>
       <c r="P60">
-        <v>-4.197171173877551</v>
+        <v>-4.311109733877553</v>
       </c>
       <c r="Q60">
-        <v>-0.007171173877551951</v>
+        <v>-0.1211097338775531</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1120243345764615</v>
+        <v>0.1136395622490582</v>
       </c>
       <c r="T60">
-        <v>1.290835544184362</v>
+        <v>1.322319337944956</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07297536454863372</v>
+        <v>0.07173849396306364</v>
       </c>
       <c r="W60">
-        <v>0.2185924090394322</v>
+        <v>0.2188840631235096</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3648768227431686</v>
+        <v>0.3586924698153182</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1757338177649845</v>
+        <v>0.1776338177649845</v>
       </c>
       <c r="C61">
-        <v>-18.63713812802185</v>
+        <v>-19.40830189472733</v>
       </c>
       <c r="D61">
-        <v>11.59886187197815</v>
+        <v>11.43169810527267</v>
       </c>
       <c r="E61">
-        <v>17.336</v>
+        <v>17.94</v>
       </c>
       <c r="F61">
-        <v>35.636</v>
+        <v>36.24</v>
       </c>
       <c r="G61">
         <v>5.4</v>
@@ -6289,37 +6289,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M61">
-        <v>8.402968800000002</v>
+        <v>8.545392000000001</v>
       </c>
       <c r="N61">
-        <v>-5.38888716734694</v>
+        <v>-5.53131036734694</v>
       </c>
       <c r="O61">
-        <v>-1.077777433469388</v>
+        <v>-1.106262073469388</v>
       </c>
       <c r="P61">
-        <v>-4.311109733877553</v>
+        <v>-4.425048293877552</v>
       </c>
       <c r="Q61">
-        <v>-0.1211097338775531</v>
+        <v>-0.2350482938775524</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1136395622490582</v>
+        <v>0.1153355513052846</v>
       </c>
       <c r="T61">
-        <v>1.322319337944956</v>
+        <v>1.35537732139358</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07173849396306364</v>
+        <v>0.07054285239701259</v>
       </c>
       <c r="W61">
-        <v>0.2188840631235096</v>
+        <v>0.2191659954047844</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3586924698153182</v>
+        <v>0.3527142619850629</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1776338177649845</v>
+        <v>0.1795338177649845</v>
       </c>
       <c r="C62">
-        <v>-19.40830189472733</v>
+        <v>-20.17471576104039</v>
       </c>
       <c r="D62">
-        <v>11.43169810527267</v>
+        <v>11.26928423895961</v>
       </c>
       <c r="E62">
-        <v>17.94</v>
+        <v>18.544</v>
       </c>
       <c r="F62">
-        <v>36.24</v>
+        <v>36.844</v>
       </c>
       <c r="G62">
         <v>5.4</v>
@@ -6371,37 +6371,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M62">
-        <v>8.545392000000001</v>
+        <v>8.687815200000001</v>
       </c>
       <c r="N62">
-        <v>-5.53131036734694</v>
+        <v>-5.67373356734694</v>
       </c>
       <c r="O62">
-        <v>-1.106262073469388</v>
+        <v>-1.134746713469388</v>
       </c>
       <c r="P62">
-        <v>-4.425048293877552</v>
+        <v>-4.538986853877551</v>
       </c>
       <c r="Q62">
-        <v>-0.2350482938775524</v>
+        <v>-0.3489868538775518</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1153355513052846</v>
+        <v>0.1171185141592663</v>
       </c>
       <c r="T62">
-        <v>1.35537732139358</v>
+        <v>1.390130586044698</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07054285239701259</v>
+        <v>0.06938641219378287</v>
       </c>
       <c r="W62">
-        <v>0.2191659954047844</v>
+        <v>0.219438684004706</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3527142619850629</v>
+        <v>0.3469320609689144</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1795338177649845</v>
+        <v>0.1814338177649845</v>
       </c>
       <c r="C63">
-        <v>-20.17471576104039</v>
+        <v>-20.9365793411331</v>
       </c>
       <c r="D63">
-        <v>11.26928423895961</v>
+        <v>11.11142065886689</v>
       </c>
       <c r="E63">
-        <v>18.544</v>
+        <v>19.148</v>
       </c>
       <c r="F63">
-        <v>36.844</v>
+        <v>37.448</v>
       </c>
       <c r="G63">
         <v>5.4</v>
@@ -6453,37 +6453,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M63">
-        <v>8.687815200000001</v>
+        <v>8.830238400000001</v>
       </c>
       <c r="N63">
-        <v>-5.67373356734694</v>
+        <v>-5.816156767346939</v>
       </c>
       <c r="O63">
-        <v>-1.134746713469388</v>
+        <v>-1.163231353469388</v>
       </c>
       <c r="P63">
-        <v>-4.538986853877551</v>
+        <v>-4.652925413877552</v>
       </c>
       <c r="Q63">
-        <v>-0.3489868538775518</v>
+        <v>-0.462925413877552</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1171185141592663</v>
+        <v>0.1189953171634575</v>
       </c>
       <c r="T63">
-        <v>1.390130586044698</v>
+        <v>1.426712969887979</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06938641219378287</v>
+        <v>0.068267276513238</v>
       </c>
       <c r="W63">
-        <v>0.219438684004706</v>
+        <v>0.2197025761981785</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3469320609689144</v>
+        <v>0.3413363825661899</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1814338177649845</v>
+        <v>0.1833338177649845</v>
       </c>
       <c r="C64">
-        <v>-20.9365793411331</v>
+        <v>-21.69408121867077</v>
       </c>
       <c r="D64">
-        <v>11.11142065886689</v>
+        <v>10.95791878132924</v>
       </c>
       <c r="E64">
-        <v>19.148</v>
+        <v>19.75200000000001</v>
       </c>
       <c r="F64">
-        <v>37.448</v>
+        <v>38.05200000000001</v>
       </c>
       <c r="G64">
         <v>5.4</v>
@@ -6535,37 +6535,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M64">
-        <v>8.830238400000001</v>
+        <v>8.972661600000002</v>
       </c>
       <c r="N64">
-        <v>-5.816156767346939</v>
+        <v>-5.958579967346941</v>
       </c>
       <c r="O64">
-        <v>-1.163231353469388</v>
+        <v>-1.191715993469388</v>
       </c>
       <c r="P64">
-        <v>-4.652925413877552</v>
+        <v>-4.766863973877553</v>
       </c>
       <c r="Q64">
-        <v>-0.462925413877552</v>
+        <v>-0.5768639738775532</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1189953171634575</v>
+        <v>0.1209735689786861</v>
       </c>
       <c r="T64">
-        <v>1.426712969887979</v>
+        <v>1.465272779884952</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.068267276513238</v>
+        <v>0.0671836689495358</v>
       </c>
       <c r="W64">
-        <v>0.2197025761981785</v>
+        <v>0.2199580908616995</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3413363825661899</v>
+        <v>0.335918344747679</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1833338177649845</v>
+        <v>0.1852338177649845</v>
       </c>
       <c r="C65">
-        <v>-21.69408121867077</v>
+        <v>-22.4473996983499</v>
       </c>
       <c r="D65">
-        <v>10.95791878132924</v>
+        <v>10.8086003016501</v>
       </c>
       <c r="E65">
-        <v>19.75200000000001</v>
+        <v>20.35600000000001</v>
       </c>
       <c r="F65">
-        <v>38.05200000000001</v>
+        <v>38.65600000000001</v>
       </c>
       <c r="G65">
         <v>5.4</v>
@@ -6617,37 +6617,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M65">
-        <v>8.972661600000002</v>
+        <v>9.115084800000002</v>
       </c>
       <c r="N65">
-        <v>-5.958579967346941</v>
+        <v>-6.10100316734694</v>
       </c>
       <c r="O65">
-        <v>-1.191715993469388</v>
+        <v>-1.220200633469388</v>
       </c>
       <c r="P65">
-        <v>-4.766863973877553</v>
+        <v>-4.880802533877552</v>
       </c>
       <c r="Q65">
-        <v>-0.5768639738775532</v>
+        <v>-0.6908025338775525</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1209735689786861</v>
+        <v>0.1230617236725385</v>
       </c>
       <c r="T65">
-        <v>1.465272779884952</v>
+        <v>1.505974801548422</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0671836689495358</v>
+        <v>0.0661339241221993</v>
       </c>
       <c r="W65">
-        <v>0.2199580908616995</v>
+        <v>0.2202056206919854</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.335918344747679</v>
+        <v>0.3306696206109965</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1852338177649845</v>
+        <v>0.1871338177649845</v>
       </c>
       <c r="C66">
-        <v>-22.4473996983499</v>
+        <v>-23.19670349681719</v>
       </c>
       <c r="D66">
-        <v>10.8086003016501</v>
+        <v>10.66329650318282</v>
       </c>
       <c r="E66">
-        <v>20.35600000000001</v>
+        <v>20.96</v>
       </c>
       <c r="F66">
-        <v>38.65600000000001</v>
+        <v>39.26000000000001</v>
       </c>
       <c r="G66">
         <v>5.4</v>
@@ -6699,37 +6699,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M66">
-        <v>9.115084800000002</v>
+        <v>9.257508000000001</v>
       </c>
       <c r="N66">
-        <v>-6.10100316734694</v>
+        <v>-6.24342636734694</v>
       </c>
       <c r="O66">
-        <v>-1.220200633469388</v>
+        <v>-1.248685273469388</v>
       </c>
       <c r="P66">
-        <v>-4.880802533877552</v>
+        <v>-4.994741093877552</v>
       </c>
       <c r="Q66">
-        <v>-0.6908025338775525</v>
+        <v>-0.8047410938775528</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1230617236725385</v>
+        <v>0.1252692014917539</v>
       </c>
       <c r="T66">
-        <v>1.505974801548422</v>
+        <v>1.549002653021235</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0661339241221993</v>
+        <v>0.06511647913570394</v>
       </c>
       <c r="W66">
-        <v>0.2202056206919854</v>
+        <v>0.220445534219801</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3306696206109965</v>
+        <v>0.3255823956785197</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1871338177649845</v>
+        <v>0.1890338177649845</v>
       </c>
       <c r="C67">
-        <v>-23.19670349681719</v>
+        <v>-23.94215237859796</v>
       </c>
       <c r="D67">
-        <v>10.66329650318282</v>
+        <v>10.52184762140205</v>
       </c>
       <c r="E67">
-        <v>20.96</v>
+        <v>21.564</v>
       </c>
       <c r="F67">
-        <v>39.26000000000001</v>
+        <v>39.864</v>
       </c>
       <c r="G67">
         <v>5.4</v>
@@ -6781,37 +6781,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M67">
-        <v>9.257508000000001</v>
+        <v>9.399931200000001</v>
       </c>
       <c r="N67">
-        <v>-6.24342636734694</v>
+        <v>-6.38584956734694</v>
       </c>
       <c r="O67">
-        <v>-1.248685273469388</v>
+        <v>-1.277169913469388</v>
       </c>
       <c r="P67">
-        <v>-4.994741093877552</v>
+        <v>-5.108679653877552</v>
       </c>
       <c r="Q67">
-        <v>-0.8047410938775528</v>
+        <v>-0.9186796538775521</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1252692014917539</v>
+        <v>0.1276065309473937</v>
       </c>
       <c r="T67">
-        <v>1.549002653021235</v>
+        <v>1.594561554580683</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06511647913570394</v>
+        <v>0.06412986581546599</v>
       </c>
       <c r="W67">
-        <v>0.220445534219801</v>
+        <v>0.2206781776407131</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3255823956785197</v>
+        <v>0.32064932907733</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1890338177649845</v>
+        <v>0.1909338177649845</v>
       </c>
       <c r="C68">
-        <v>-23.94215237859796</v>
+        <v>-24.68389774207373</v>
       </c>
       <c r="D68">
-        <v>10.52184762140205</v>
+        <v>10.38410225792628</v>
       </c>
       <c r="E68">
-        <v>21.564</v>
+        <v>22.168</v>
       </c>
       <c r="F68">
-        <v>39.864</v>
+        <v>40.468</v>
       </c>
       <c r="G68">
         <v>5.4</v>
@@ -6863,37 +6863,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M68">
-        <v>9.399931200000001</v>
+        <v>9.542354400000001</v>
       </c>
       <c r="N68">
-        <v>-6.38584956734694</v>
+        <v>-6.528272767346939</v>
       </c>
       <c r="O68">
-        <v>-1.277169913469388</v>
+        <v>-1.305654553469388</v>
       </c>
       <c r="P68">
-        <v>-5.108679653877552</v>
+        <v>-5.222618213877551</v>
       </c>
       <c r="Q68">
-        <v>-0.9186796538775521</v>
+        <v>-1.032618213877551</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1276065309473937</v>
+        <v>0.1300855167336784</v>
       </c>
       <c r="T68">
-        <v>1.594561554580683</v>
+        <v>1.642881601689188</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06412986581546599</v>
+        <v>0.06317270363911576</v>
       </c>
       <c r="W68">
-        <v>0.2206781776407131</v>
+        <v>0.2209038764818965</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.32064932907733</v>
+        <v>0.3158635181955788</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1909338177649845</v>
+        <v>0.1928338177649845</v>
       </c>
       <c r="C69">
-        <v>-24.68389774207373</v>
+        <v>-25.42208316002701</v>
       </c>
       <c r="D69">
-        <v>10.38410225792628</v>
+        <v>10.249916839973</v>
       </c>
       <c r="E69">
-        <v>22.168</v>
+        <v>22.77200000000001</v>
       </c>
       <c r="F69">
-        <v>40.468</v>
+        <v>41.07200000000001</v>
       </c>
       <c r="G69">
         <v>5.4</v>
@@ -6945,37 +6945,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M69">
-        <v>9.542354400000001</v>
+        <v>9.684777600000002</v>
       </c>
       <c r="N69">
-        <v>-6.528272767346939</v>
+        <v>-6.670695967346941</v>
       </c>
       <c r="O69">
-        <v>-1.305654553469388</v>
+        <v>-1.334139193469388</v>
       </c>
       <c r="P69">
-        <v>-5.222618213877551</v>
+        <v>-5.336556773877552</v>
       </c>
       <c r="Q69">
-        <v>-1.032618213877551</v>
+        <v>-1.146556773877553</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1300855167336784</v>
+        <v>0.1327194391316058</v>
       </c>
       <c r="T69">
-        <v>1.642881601689188</v>
+        <v>1.694221651741976</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06317270363911576</v>
+        <v>0.0622436932914817</v>
       </c>
       <c r="W69">
-        <v>0.2209038764818965</v>
+        <v>0.2211229371218686</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3158635181955788</v>
+        <v>0.3112184664574085</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1928338177649845</v>
+        <v>0.1947338177649845</v>
       </c>
       <c r="C70">
-        <v>-25.42208316002701</v>
+        <v>-26.15684487881057</v>
       </c>
       <c r="D70">
-        <v>10.249916839973</v>
+        <v>10.11915512118943</v>
       </c>
       <c r="E70">
-        <v>22.77200000000001</v>
+        <v>23.37600000000001</v>
       </c>
       <c r="F70">
-        <v>41.07200000000001</v>
+        <v>41.67600000000001</v>
       </c>
       <c r="G70">
         <v>5.4</v>
@@ -7027,37 +7027,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M70">
-        <v>9.684777600000002</v>
+        <v>9.827200800000002</v>
       </c>
       <c r="N70">
-        <v>-6.670695967346941</v>
+        <v>-6.81311916734694</v>
       </c>
       <c r="O70">
-        <v>-1.334139193469388</v>
+        <v>-1.362623833469388</v>
       </c>
       <c r="P70">
-        <v>-5.336556773877552</v>
+        <v>-5.450495333877552</v>
       </c>
       <c r="Q70">
-        <v>-1.146556773877553</v>
+        <v>-1.260495333877553</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1327194391316058</v>
+        <v>0.1355232920068189</v>
       </c>
       <c r="T70">
-        <v>1.694221651741976</v>
+        <v>1.748873963088491</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0622436932914817</v>
+        <v>0.06134161078001095</v>
       </c>
       <c r="W70">
-        <v>0.2211229371218686</v>
+        <v>0.2213356481780734</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3112184664574085</v>
+        <v>0.3067080539000547</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1947338177649845</v>
+        <v>0.1966338177649845</v>
       </c>
       <c r="C71">
-        <v>-26.15684487881057</v>
+        <v>-26.88831227978969</v>
       </c>
       <c r="D71">
-        <v>10.11915512118943</v>
+        <v>9.991687720210313</v>
       </c>
       <c r="E71">
-        <v>23.37600000000001</v>
+        <v>23.98000000000001</v>
       </c>
       <c r="F71">
-        <v>41.67600000000001</v>
+        <v>42.28000000000001</v>
       </c>
       <c r="G71">
         <v>5.4</v>
@@ -7109,37 +7109,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M71">
-        <v>9.827200800000002</v>
+        <v>9.969624000000003</v>
       </c>
       <c r="N71">
-        <v>-6.81311916734694</v>
+        <v>-6.955542367346942</v>
       </c>
       <c r="O71">
-        <v>-1.362623833469388</v>
+        <v>-1.391108473469388</v>
       </c>
       <c r="P71">
-        <v>-5.450495333877552</v>
+        <v>-5.564433893877553</v>
       </c>
       <c r="Q71">
-        <v>-1.260495333877553</v>
+        <v>-1.374433893877554</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1355232920068189</v>
+        <v>0.1385140684070462</v>
       </c>
       <c r="T71">
-        <v>1.748873963088491</v>
+        <v>1.807169761858107</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06134161078001095</v>
+        <v>0.06046530205458222</v>
       </c>
       <c r="W71">
-        <v>0.2213356481780734</v>
+        <v>0.2215422817755295</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3067080539000547</v>
+        <v>0.302326510272911</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1966338177649845</v>
+        <v>0.1985338177649845</v>
       </c>
       <c r="C72">
-        <v>-26.88831227978969</v>
+        <v>-27.61660830634231</v>
       </c>
       <c r="D72">
-        <v>9.991687720210313</v>
+        <v>9.867391693657698</v>
       </c>
       <c r="E72">
-        <v>23.98000000000001</v>
+        <v>24.58400000000001</v>
       </c>
       <c r="F72">
-        <v>42.28000000000001</v>
+        <v>42.88400000000001</v>
       </c>
       <c r="G72">
         <v>5.4</v>
@@ -7191,37 +7191,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M72">
-        <v>9.969624000000003</v>
+        <v>10.1120472</v>
       </c>
       <c r="N72">
-        <v>-6.955542367346942</v>
+        <v>-7.097965567346941</v>
       </c>
       <c r="O72">
-        <v>-1.391108473469388</v>
+        <v>-1.419593113469388</v>
       </c>
       <c r="P72">
-        <v>-5.564433893877553</v>
+        <v>-5.678372453877553</v>
       </c>
       <c r="Q72">
-        <v>-1.374433893877554</v>
+        <v>-1.488372453877553</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1385140684070462</v>
+        <v>0.1417111052486685</v>
       </c>
       <c r="T72">
-        <v>1.807169761858107</v>
+        <v>1.86948596054287</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06046530205458222</v>
+        <v>0.05961367808198246</v>
       </c>
       <c r="W72">
-        <v>0.2215422817755295</v>
+        <v>0.2217430947082685</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.302326510272911</v>
+        <v>0.2980683904099123</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1985338177649845</v>
+        <v>0.2004338177649845</v>
       </c>
       <c r="C73">
-        <v>-27.6166083063423</v>
+        <v>-28.34184985937983</v>
       </c>
       <c r="D73">
-        <v>9.867391693657698</v>
+        <v>9.746150140620164</v>
       </c>
       <c r="E73">
-        <v>24.584</v>
+        <v>25.188</v>
       </c>
       <c r="F73">
-        <v>42.884</v>
+        <v>43.488</v>
       </c>
       <c r="G73">
         <v>5.4</v>
@@ -7273,37 +7273,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M73">
-        <v>10.1120472</v>
+        <v>10.2544704</v>
       </c>
       <c r="N73">
-        <v>-7.09796556734694</v>
+        <v>-7.240388767346939</v>
       </c>
       <c r="O73">
-        <v>-1.419593113469388</v>
+        <v>-1.448077753469388</v>
       </c>
       <c r="P73">
-        <v>-5.678372453877552</v>
+        <v>-5.792311013877551</v>
       </c>
       <c r="Q73">
-        <v>-1.488372453877552</v>
+        <v>-1.602311013877552</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1417111052486685</v>
+        <v>0.1451365018646923</v>
       </c>
       <c r="T73">
-        <v>1.869485960542869</v>
+        <v>1.936253316276543</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05961367808198247</v>
+        <v>0.05878571033084384</v>
       </c>
       <c r="W73">
-        <v>0.2217430947082685</v>
+        <v>0.221938329503987</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2980683904099124</v>
+        <v>0.2939285516542192</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2004338177649845</v>
+        <v>0.2023338177649845</v>
       </c>
       <c r="C74">
-        <v>-28.34184985937983</v>
+        <v>-29.06414816406299</v>
       </c>
       <c r="D74">
-        <v>9.746150140620164</v>
+        <v>9.627851835937014</v>
       </c>
       <c r="E74">
-        <v>25.188</v>
+        <v>25.79200000000001</v>
       </c>
       <c r="F74">
-        <v>43.488</v>
+        <v>44.09200000000001</v>
       </c>
       <c r="G74">
         <v>5.4</v>
@@ -7355,37 +7355,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M74">
-        <v>10.2544704</v>
+        <v>10.3968936</v>
       </c>
       <c r="N74">
-        <v>-7.240388767346939</v>
+        <v>-7.382811967346941</v>
       </c>
       <c r="O74">
-        <v>-1.448077753469388</v>
+        <v>-1.476562393469388</v>
       </c>
       <c r="P74">
-        <v>-5.792311013877551</v>
+        <v>-5.906249573877552</v>
       </c>
       <c r="Q74">
-        <v>-1.602311013877552</v>
+        <v>-1.716249573877553</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1451365018646923</v>
+        <v>0.1488156315633846</v>
       </c>
       <c r="T74">
-        <v>1.936253316276543</v>
+        <v>2.007966402064563</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05878571033084384</v>
+        <v>0.05798042662768158</v>
       </c>
       <c r="W74">
-        <v>0.221938329503987</v>
+        <v>0.2221282154011927</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2939285516542192</v>
+        <v>0.2899021331384078</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2023338177649845</v>
+        <v>0.2042338177649845</v>
       </c>
       <c r="C75">
-        <v>-29.06414816406299</v>
+        <v>-29.7836091101308</v>
       </c>
       <c r="D75">
-        <v>9.627851835937014</v>
+        <v>9.512390889869206</v>
       </c>
       <c r="E75">
-        <v>25.79200000000001</v>
+        <v>26.396</v>
       </c>
       <c r="F75">
-        <v>44.09200000000001</v>
+        <v>44.69600000000001</v>
       </c>
       <c r="G75">
         <v>5.4</v>
@@ -7437,37 +7437,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M75">
-        <v>10.3968936</v>
+        <v>10.5393168</v>
       </c>
       <c r="N75">
-        <v>-7.382811967346941</v>
+        <v>-7.52523516734694</v>
       </c>
       <c r="O75">
-        <v>-1.476562393469388</v>
+        <v>-1.505047033469388</v>
       </c>
       <c r="P75">
-        <v>-5.906249573877552</v>
+        <v>-6.020188133877552</v>
       </c>
       <c r="Q75">
-        <v>-1.716249573877553</v>
+        <v>-1.830188133877552</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1488156315633846</v>
+        <v>0.1527777712388994</v>
       </c>
       <c r="T75">
-        <v>2.007966402064563</v>
+        <v>2.085195879067046</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05798042662768158</v>
+        <v>0.05719690734892913</v>
       </c>
       <c r="W75">
-        <v>0.2221282154011927</v>
+        <v>0.2223129692471225</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2899021331384078</v>
+        <v>0.2859845367446456</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2042338177649845</v>
+        <v>0.2061338177649845</v>
       </c>
       <c r="C76">
-        <v>-29.7836091101308</v>
+        <v>-30.50033356803177</v>
       </c>
       <c r="D76">
-        <v>9.512390889869206</v>
+        <v>9.399666431968232</v>
       </c>
       <c r="E76">
-        <v>26.396</v>
+        <v>27</v>
       </c>
       <c r="F76">
-        <v>44.69600000000001</v>
+        <v>45.3</v>
       </c>
       <c r="G76">
         <v>5.4</v>
@@ -7519,37 +7519,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M76">
-        <v>10.5393168</v>
+        <v>10.68174</v>
       </c>
       <c r="N76">
-        <v>-7.52523516734694</v>
+        <v>-7.66765836734694</v>
       </c>
       <c r="O76">
-        <v>-1.505047033469388</v>
+        <v>-1.533531673469388</v>
       </c>
       <c r="P76">
-        <v>-6.020188133877552</v>
+        <v>-6.134126693877552</v>
       </c>
       <c r="Q76">
-        <v>-1.830188133877552</v>
+        <v>-1.944126693877553</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1527777712388994</v>
+        <v>0.1570568820884554</v>
       </c>
       <c r="T76">
-        <v>2.085195879067046</v>
+        <v>2.168603714229729</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05719690734892913</v>
+        <v>0.05643428191761007</v>
       </c>
       <c r="W76">
-        <v>0.2223129692471225</v>
+        <v>0.2224927963238276</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2859845367446456</v>
+        <v>0.2821714095880503</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2061338177649845</v>
+        <v>0.2080338177649845</v>
       </c>
       <c r="C77">
-        <v>-30.50033356803177</v>
+        <v>-31.21441768284075</v>
       </c>
       <c r="D77">
-        <v>9.399666431968232</v>
+        <v>9.289582317159249</v>
       </c>
       <c r="E77">
-        <v>27</v>
+        <v>27.604</v>
       </c>
       <c r="F77">
-        <v>45.3</v>
+        <v>45.904</v>
       </c>
       <c r="G77">
         <v>5.4</v>
@@ -7601,37 +7601,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M77">
-        <v>10.68174</v>
+        <v>10.8241632</v>
       </c>
       <c r="N77">
-        <v>-7.66765836734694</v>
+        <v>-7.810081567346939</v>
       </c>
       <c r="O77">
-        <v>-1.533531673469388</v>
+        <v>-1.562016313469388</v>
       </c>
       <c r="P77">
-        <v>-6.134126693877552</v>
+        <v>-6.248065253877551</v>
       </c>
       <c r="Q77">
-        <v>-1.944126693877553</v>
+        <v>-2.058065253877552</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1570568820884554</v>
+        <v>0.1616925855088077</v>
       </c>
       <c r="T77">
-        <v>2.168603714229729</v>
+        <v>2.258962202322634</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05643428191761007</v>
+        <v>0.05569172557658889</v>
       </c>
       <c r="W77">
-        <v>0.2224927963238276</v>
+        <v>0.2226678911090404</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2821714095880503</v>
+        <v>0.2784586278829444</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2080338177649845</v>
+        <v>0.2099338177649845</v>
       </c>
       <c r="C78">
-        <v>-31.21441768284075</v>
+        <v>-31.92595314776166</v>
       </c>
       <c r="D78">
-        <v>9.289582317159249</v>
+        <v>9.182046852238338</v>
       </c>
       <c r="E78">
-        <v>27.604</v>
+        <v>28.208</v>
       </c>
       <c r="F78">
-        <v>45.904</v>
+        <v>46.508</v>
       </c>
       <c r="G78">
         <v>5.4</v>
@@ -7683,37 +7683,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M78">
-        <v>10.8241632</v>
+        <v>10.9665864</v>
       </c>
       <c r="N78">
-        <v>-7.810081567346939</v>
+        <v>-7.952504767346939</v>
       </c>
       <c r="O78">
-        <v>-1.562016313469388</v>
+        <v>-1.590500953469388</v>
       </c>
       <c r="P78">
-        <v>-6.248065253877551</v>
+        <v>-6.362003813877552</v>
       </c>
       <c r="Q78">
-        <v>-2.058065253877552</v>
+        <v>-2.172003813877552</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1616925855088077</v>
+        <v>0.1667313935744081</v>
       </c>
       <c r="T78">
-        <v>2.258962202322634</v>
+        <v>2.357177950249705</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05569172557658889</v>
+        <v>0.05496845641325657</v>
       </c>
       <c r="W78">
-        <v>0.2226678911090404</v>
+        <v>0.2228384379777541</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2784586278829444</v>
+        <v>0.2748422820662828</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2099338177649845</v>
+        <v>0.2118338177649845</v>
       </c>
       <c r="C79">
-        <v>-31.92595314776166</v>
+        <v>-32.6350274588514</v>
       </c>
       <c r="D79">
-        <v>9.182046852238338</v>
+        <v>9.076972541148608</v>
       </c>
       <c r="E79">
-        <v>28.208</v>
+        <v>28.81200000000001</v>
       </c>
       <c r="F79">
-        <v>46.508</v>
+        <v>47.11200000000001</v>
       </c>
       <c r="G79">
         <v>5.4</v>
@@ -7765,37 +7765,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M79">
-        <v>10.9665864</v>
+        <v>11.1090096</v>
       </c>
       <c r="N79">
-        <v>-7.952504767346939</v>
+        <v>-8.094927967346941</v>
       </c>
       <c r="O79">
-        <v>-1.590500953469388</v>
+        <v>-1.618985593469388</v>
       </c>
       <c r="P79">
-        <v>-6.362003813877552</v>
+        <v>-6.475942373877553</v>
       </c>
       <c r="Q79">
-        <v>-2.172003813877552</v>
+        <v>-2.285942373877553</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1667313935744081</v>
+        <v>0.1722282751005176</v>
       </c>
       <c r="T79">
-        <v>2.357177950249705</v>
+        <v>2.464322402533783</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05496845641325657</v>
+        <v>0.0542637326130866</v>
       </c>
       <c r="W79">
-        <v>0.2228384379777541</v>
+        <v>0.2230046118498342</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2748422820662828</v>
+        <v>0.2713186630654331</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2118338177649845</v>
+        <v>0.2137338177649846</v>
       </c>
       <c r="C80">
-        <v>-32.6350274588514</v>
+        <v>-33.34172415245196</v>
       </c>
       <c r="D80">
-        <v>9.076972541148608</v>
+        <v>8.974275847548048</v>
       </c>
       <c r="E80">
-        <v>28.81200000000001</v>
+        <v>29.41600000000001</v>
       </c>
       <c r="F80">
-        <v>47.11200000000001</v>
+        <v>47.71600000000001</v>
       </c>
       <c r="G80">
         <v>5.4</v>
@@ -7847,37 +7847,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M80">
-        <v>11.1090096</v>
+        <v>11.2514328</v>
       </c>
       <c r="N80">
-        <v>-8.094927967346941</v>
+        <v>-8.23735116734694</v>
       </c>
       <c r="O80">
-        <v>-1.618985593469388</v>
+        <v>-1.647470233469388</v>
       </c>
       <c r="P80">
-        <v>-6.475942373877553</v>
+        <v>-6.589880933877552</v>
       </c>
       <c r="Q80">
-        <v>-2.285942373877553</v>
+        <v>-2.399880933877553</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1722282751005176</v>
+        <v>0.1782486691529231</v>
       </c>
       <c r="T80">
-        <v>2.464322402533783</v>
+        <v>2.581671088368725</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0542637326130866</v>
+        <v>0.05357684992178172</v>
       </c>
       <c r="W80">
-        <v>0.2230046118498342</v>
+        <v>0.2231665787884439</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2713186630654331</v>
+        <v>0.2678842496089086</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2137338177649846</v>
+        <v>0.2156338177649845</v>
       </c>
       <c r="C81">
-        <v>-33.34172415245196</v>
+        <v>-34.04612302668522</v>
       </c>
       <c r="D81">
-        <v>8.974275847548048</v>
+        <v>8.87387697331479</v>
       </c>
       <c r="E81">
-        <v>29.41600000000001</v>
+        <v>30.02000000000001</v>
       </c>
       <c r="F81">
-        <v>47.71600000000001</v>
+        <v>48.32000000000001</v>
       </c>
       <c r="G81">
         <v>5.4</v>
@@ -7929,37 +7929,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M81">
-        <v>11.2514328</v>
+        <v>11.393856</v>
       </c>
       <c r="N81">
-        <v>-8.23735116734694</v>
+        <v>-8.379774367346942</v>
       </c>
       <c r="O81">
-        <v>-1.647470233469388</v>
+        <v>-1.675954873469388</v>
       </c>
       <c r="P81">
-        <v>-6.589880933877552</v>
+        <v>-6.703819493877553</v>
       </c>
       <c r="Q81">
-        <v>-2.399880933877553</v>
+        <v>-2.513819493877554</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1782486691529231</v>
+        <v>0.1848711026105693</v>
       </c>
       <c r="T81">
-        <v>2.581671088368725</v>
+        <v>2.710754642787161</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05357684992178172</v>
+        <v>0.05290713929775943</v>
       </c>
       <c r="W81">
-        <v>0.2231665787884439</v>
+        <v>0.2233244965535883</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2678842496089086</v>
+        <v>0.2645356964887972</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2156338177649845</v>
+        <v>0.2175338177649845</v>
       </c>
       <c r="C82">
-        <v>-34.04612302668522</v>
+        <v>-34.74830034824439</v>
       </c>
       <c r="D82">
-        <v>8.87387697331479</v>
+        <v>8.775699651755613</v>
       </c>
       <c r="E82">
-        <v>30.02000000000001</v>
+        <v>30.62400000000001</v>
       </c>
       <c r="F82">
-        <v>48.32000000000001</v>
+        <v>48.92400000000001</v>
       </c>
       <c r="G82">
         <v>5.4</v>
@@ -8011,37 +8011,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M82">
-        <v>11.393856</v>
+        <v>11.5362792</v>
       </c>
       <c r="N82">
-        <v>-8.379774367346942</v>
+        <v>-8.522197567346941</v>
       </c>
       <c r="O82">
-        <v>-1.675954873469388</v>
+        <v>-1.704439513469388</v>
       </c>
       <c r="P82">
-        <v>-6.703819493877553</v>
+        <v>-6.817758053877553</v>
       </c>
       <c r="Q82">
-        <v>-2.513819493877554</v>
+        <v>-2.627758053877553</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1848711026105693</v>
+        <v>0.192190634326915</v>
       </c>
       <c r="T82">
-        <v>2.710754642787161</v>
+        <v>2.853425939775959</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05290713929775943</v>
+        <v>0.05225396473852784</v>
       </c>
       <c r="W82">
-        <v>0.2233244965535883</v>
+        <v>0.2234785151146551</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2645356964887972</v>
+        <v>0.2612698236926392</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2175338177649845</v>
+        <v>0.2194338177649846</v>
       </c>
       <c r="C83">
-        <v>-34.74830034824439</v>
+        <v>-35.44832904560855</v>
       </c>
       <c r="D83">
-        <v>8.775699651755613</v>
+        <v>8.679670954391462</v>
       </c>
       <c r="E83">
-        <v>30.62400000000001</v>
+        <v>31.22800000000001</v>
       </c>
       <c r="F83">
-        <v>48.92400000000001</v>
+        <v>49.52800000000001</v>
       </c>
       <c r="G83">
         <v>5.4</v>
@@ -8093,37 +8093,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M83">
-        <v>11.5362792</v>
+        <v>11.6787024</v>
       </c>
       <c r="N83">
-        <v>-8.522197567346941</v>
+        <v>-8.664620767346941</v>
       </c>
       <c r="O83">
-        <v>-1.704439513469388</v>
+        <v>-1.732924153469388</v>
       </c>
       <c r="P83">
-        <v>-6.817758053877553</v>
+        <v>-6.931696613877553</v>
       </c>
       <c r="Q83">
-        <v>-2.627758053877553</v>
+        <v>-2.741696613877553</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.192190634326915</v>
+        <v>0.200323447345077</v>
       </c>
       <c r="T83">
-        <v>2.853425939775959</v>
+        <v>3.011949603096846</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05225396473852784</v>
+        <v>0.05161672126610677</v>
       </c>
       <c r="W83">
-        <v>0.2234785151146551</v>
+        <v>0.223628777125452</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2612698236926392</v>
+        <v>0.2580836063305338</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2194338177649846</v>
+        <v>0.2213338177649845</v>
       </c>
       <c r="C84">
-        <v>-35.44832904560855</v>
+        <v>-36.14627888970881</v>
       </c>
       <c r="D84">
-        <v>8.679670954391462</v>
+        <v>8.585721110291203</v>
       </c>
       <c r="E84">
-        <v>31.22800000000001</v>
+        <v>31.83200000000001</v>
       </c>
       <c r="F84">
-        <v>49.52800000000001</v>
+        <v>50.13200000000001</v>
       </c>
       <c r="G84">
         <v>5.4</v>
@@ -8175,37 +8175,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M84">
-        <v>11.6787024</v>
+        <v>11.8211256</v>
       </c>
       <c r="N84">
-        <v>-8.664620767346941</v>
+        <v>-8.807043967346942</v>
       </c>
       <c r="O84">
-        <v>-1.732924153469388</v>
+        <v>-1.761408793469389</v>
       </c>
       <c r="P84">
-        <v>-6.931696613877553</v>
+        <v>-7.045635173877554</v>
       </c>
       <c r="Q84">
-        <v>-2.741696613877553</v>
+        <v>-2.855635173877555</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.200323447345077</v>
+        <v>0.2094130618947874</v>
       </c>
       <c r="T84">
-        <v>3.011949603096846</v>
+        <v>3.189123109161366</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05161672126610677</v>
+        <v>0.05099483305808138</v>
       </c>
       <c r="W84">
-        <v>0.223628777125452</v>
+        <v>0.2237754183649044</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2580836063305338</v>
+        <v>0.254974165290407</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2213338177649845</v>
+        <v>0.2232338177649845</v>
       </c>
       <c r="C85">
-        <v>-36.14627888970881</v>
+        <v>-36.84221666298696</v>
       </c>
       <c r="D85">
-        <v>8.585721110291203</v>
+        <v>8.493783337013054</v>
       </c>
       <c r="E85">
-        <v>31.83200000000001</v>
+        <v>32.43600000000001</v>
       </c>
       <c r="F85">
-        <v>50.13200000000001</v>
+        <v>50.73600000000001</v>
       </c>
       <c r="G85">
         <v>5.4</v>
@@ -8257,37 +8257,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M85">
-        <v>11.8211256</v>
+        <v>11.9635488</v>
       </c>
       <c r="N85">
-        <v>-8.807043967346942</v>
+        <v>-8.949467167346942</v>
       </c>
       <c r="O85">
-        <v>-1.761408793469389</v>
+        <v>-1.789893433469389</v>
       </c>
       <c r="P85">
-        <v>-7.045635173877554</v>
+        <v>-7.159573733877553</v>
       </c>
       <c r="Q85">
-        <v>-2.855635173877555</v>
+        <v>-2.969573733877554</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2094130618947874</v>
+        <v>0.2196388782632117</v>
       </c>
       <c r="T85">
-        <v>3.189123109161366</v>
+        <v>3.388443303483953</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05099483305808138</v>
+        <v>0.05038775171215185</v>
       </c>
       <c r="W85">
-        <v>0.2237754183649044</v>
+        <v>0.2239185681462746</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.254974165290407</v>
+        <v>0.2519387585607592</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2232338177649845</v>
+        <v>0.2251338177649845</v>
       </c>
       <c r="C86">
-        <v>-36.84221666298695</v>
+        <v>-37.53620631770714</v>
       </c>
       <c r="D86">
-        <v>8.493783337013054</v>
+        <v>8.403793682292864</v>
       </c>
       <c r="E86">
-        <v>32.43600000000001</v>
+        <v>33.04000000000001</v>
       </c>
       <c r="F86">
-        <v>50.736</v>
+        <v>51.34</v>
       </c>
       <c r="G86">
         <v>5.4</v>
@@ -8339,37 +8339,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M86">
-        <v>11.9635488</v>
+        <v>12.105972</v>
       </c>
       <c r="N86">
-        <v>-8.94946716734694</v>
+        <v>-9.09189036734694</v>
       </c>
       <c r="O86">
-        <v>-1.789893433469388</v>
+        <v>-1.818378073469388</v>
       </c>
       <c r="P86">
-        <v>-7.159573733877552</v>
+        <v>-7.273512293877552</v>
       </c>
       <c r="Q86">
-        <v>-2.969573733877553</v>
+        <v>-3.083512293877552</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2196388782632116</v>
+        <v>0.2312281368140923</v>
       </c>
       <c r="T86">
-        <v>3.388443303483951</v>
+        <v>3.614339523716214</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05038775171215185</v>
+        <v>0.04979495463318537</v>
       </c>
       <c r="W86">
-        <v>0.2239185681462746</v>
+        <v>0.2240583496974949</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2519387585607592</v>
+        <v>0.2489747731659268</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2251338177649845</v>
+        <v>0.2270338177649845</v>
       </c>
       <c r="C87">
-        <v>-37.53620631770714</v>
+        <v>-38.2283091243095</v>
       </c>
       <c r="D87">
-        <v>8.403793682292864</v>
+        <v>8.3156908756905</v>
       </c>
       <c r="E87">
-        <v>33.04000000000001</v>
+        <v>33.64400000000001</v>
       </c>
       <c r="F87">
-        <v>51.34</v>
+        <v>51.944</v>
       </c>
       <c r="G87">
         <v>5.4</v>
@@ -8421,37 +8421,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M87">
-        <v>12.105972</v>
+        <v>12.2483952</v>
       </c>
       <c r="N87">
-        <v>-9.09189036734694</v>
+        <v>-9.234313567346939</v>
       </c>
       <c r="O87">
-        <v>-1.818378073469388</v>
+        <v>-1.846862713469388</v>
       </c>
       <c r="P87">
-        <v>-7.273512293877552</v>
+        <v>-7.387450853877551</v>
       </c>
       <c r="Q87">
-        <v>-3.083512293877552</v>
+        <v>-3.197450853877552</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2312281368140923</v>
+        <v>0.2444730037293847</v>
       </c>
       <c r="T87">
-        <v>3.614339523716214</v>
+        <v>3.872506632553086</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04979495463318537</v>
+        <v>0.04921594353279948</v>
       </c>
       <c r="W87">
-        <v>0.2240583496974949</v>
+        <v>0.2241948805149659</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2489747731659268</v>
+        <v>0.2460797176639974</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2270338177649845</v>
+        <v>0.2289338177649845</v>
       </c>
       <c r="C88">
-        <v>-38.2283091243095</v>
+        <v>-38.91858381052878</v>
       </c>
       <c r="D88">
-        <v>8.3156908756905</v>
+        <v>8.229416189471223</v>
       </c>
       <c r="E88">
-        <v>33.64400000000001</v>
+        <v>34.248</v>
       </c>
       <c r="F88">
-        <v>51.944</v>
+        <v>52.548</v>
       </c>
       <c r="G88">
         <v>5.4</v>
@@ -8503,37 +8503,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M88">
-        <v>12.2483952</v>
+        <v>12.3908184</v>
       </c>
       <c r="N88">
-        <v>-9.234313567346939</v>
+        <v>-9.376736767346939</v>
       </c>
       <c r="O88">
-        <v>-1.846862713469388</v>
+        <v>-1.875347353469388</v>
       </c>
       <c r="P88">
-        <v>-7.387450853877551</v>
+        <v>-7.501389413877551</v>
       </c>
       <c r="Q88">
-        <v>-3.197450853877552</v>
+        <v>-3.311389413877552</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2444730037293847</v>
+        <v>0.2597555424777989</v>
       </c>
       <c r="T88">
-        <v>3.872506632553086</v>
+        <v>4.170391758134093</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04921594353279948</v>
+        <v>0.04865024303242248</v>
       </c>
       <c r="W88">
-        <v>0.2241948805149659</v>
+        <v>0.2243282726929548</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2460797176639974</v>
+        <v>0.2432512151621125</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2289338177649845</v>
+        <v>0.2308338177649845</v>
       </c>
       <c r="C89">
-        <v>-38.91858381052878</v>
+        <v>-39.60708669194182</v>
       </c>
       <c r="D89">
-        <v>8.229416189471223</v>
+        <v>8.144913308058189</v>
       </c>
       <c r="E89">
-        <v>34.248</v>
+        <v>34.852</v>
       </c>
       <c r="F89">
-        <v>52.548</v>
+        <v>53.15200000000001</v>
       </c>
       <c r="G89">
         <v>5.4</v>
@@ -8585,37 +8585,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M89">
-        <v>12.3908184</v>
+        <v>12.5332416</v>
       </c>
       <c r="N89">
-        <v>-9.376736767346939</v>
+        <v>-9.51915996734694</v>
       </c>
       <c r="O89">
-        <v>-1.875347353469388</v>
+        <v>-1.903831993469388</v>
       </c>
       <c r="P89">
-        <v>-7.501389413877551</v>
+        <v>-7.615327973877553</v>
       </c>
       <c r="Q89">
-        <v>-3.311389413877552</v>
+        <v>-3.425327973877553</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2597555424777989</v>
+        <v>0.2775851710176155</v>
       </c>
       <c r="T89">
-        <v>4.170391758134093</v>
+        <v>4.517924404645268</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04865024303242248</v>
+        <v>0.04809739936159949</v>
       </c>
       <c r="W89">
-        <v>0.2243282726929548</v>
+        <v>0.2244586332305348</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2432512151621125</v>
+        <v>0.2404869968079975</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2308338177649845</v>
+        <v>0.2327338177649845</v>
       </c>
       <c r="C90">
-        <v>-39.60708669194182</v>
+        <v>-40.29387179455372</v>
       </c>
       <c r="D90">
-        <v>8.144913308058189</v>
+        <v>8.06212820544628</v>
       </c>
       <c r="E90">
-        <v>34.852</v>
+        <v>35.456</v>
       </c>
       <c r="F90">
-        <v>53.15200000000001</v>
+        <v>53.75600000000001</v>
       </c>
       <c r="G90">
         <v>5.4</v>
@@ -8667,37 +8667,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M90">
-        <v>12.5332416</v>
+        <v>12.6756648</v>
       </c>
       <c r="N90">
-        <v>-9.51915996734694</v>
+        <v>-9.66158316734694</v>
       </c>
       <c r="O90">
-        <v>-1.903831993469388</v>
+        <v>-1.932316633469388</v>
       </c>
       <c r="P90">
-        <v>-7.615327973877553</v>
+        <v>-7.729266533877552</v>
       </c>
       <c r="Q90">
-        <v>-3.425327973877553</v>
+        <v>-3.539266533877552</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2775851710176155</v>
+        <v>0.2986565502010351</v>
       </c>
       <c r="T90">
-        <v>4.517924404645268</v>
+        <v>4.928644805067566</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04809739936159949</v>
+        <v>0.04755697914405344</v>
       </c>
       <c r="W90">
-        <v>0.2244586332305348</v>
+        <v>0.2245860643178322</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2404869968079975</v>
+        <v>0.2377848957202672</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2327338177649845</v>
+        <v>0.2346338177649845</v>
       </c>
       <c r="C91">
-        <v>-40.29387179455372</v>
+        <v>-40.97899096998349</v>
       </c>
       <c r="D91">
-        <v>8.06212820544628</v>
+        <v>7.981009030016526</v>
       </c>
       <c r="E91">
-        <v>35.456</v>
+        <v>36.06</v>
       </c>
       <c r="F91">
-        <v>53.75600000000001</v>
+        <v>54.36000000000001</v>
       </c>
       <c r="G91">
         <v>5.4</v>
@@ -8749,37 +8749,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M91">
-        <v>12.6756648</v>
+        <v>12.818088</v>
       </c>
       <c r="N91">
-        <v>-9.66158316734694</v>
+        <v>-9.80400636734694</v>
       </c>
       <c r="O91">
-        <v>-1.932316633469388</v>
+        <v>-1.960801273469388</v>
       </c>
       <c r="P91">
-        <v>-7.729266533877552</v>
+        <v>-7.843205093877552</v>
       </c>
       <c r="Q91">
-        <v>-3.539266533877552</v>
+        <v>-3.653205093877553</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2986565502010351</v>
+        <v>0.3239422052211386</v>
       </c>
       <c r="T91">
-        <v>4.928644805067566</v>
+        <v>5.421509285574323</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04755697914405344</v>
+        <v>0.04702856826467507</v>
       </c>
       <c r="W91">
-        <v>0.2245860643178322</v>
+        <v>0.2247106636031896</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2377848957202672</v>
+        <v>0.2351428413233753</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2346338177649845</v>
+        <v>0.2365338177649846</v>
       </c>
       <c r="C92">
-        <v>-40.97899096998349</v>
+        <v>-41.66249400376492</v>
       </c>
       <c r="D92">
-        <v>7.981009030016526</v>
+        <v>7.901505996235088</v>
       </c>
       <c r="E92">
-        <v>36.06</v>
+        <v>36.664</v>
       </c>
       <c r="F92">
-        <v>54.36000000000001</v>
+        <v>54.96400000000001</v>
       </c>
       <c r="G92">
         <v>5.4</v>
@@ -8831,37 +8831,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M92">
-        <v>12.818088</v>
+        <v>12.9605112</v>
       </c>
       <c r="N92">
-        <v>-9.80400636734694</v>
+        <v>-9.946429567346941</v>
       </c>
       <c r="O92">
-        <v>-1.960801273469388</v>
+        <v>-1.989285913469388</v>
       </c>
       <c r="P92">
-        <v>-7.843205093877552</v>
+        <v>-7.957143653877553</v>
       </c>
       <c r="Q92">
-        <v>-3.653205093877553</v>
+        <v>-3.767143653877554</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3239422052211386</v>
+        <v>0.3548468946901541</v>
       </c>
       <c r="T92">
-        <v>5.421509285574323</v>
+        <v>6.023899206193692</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04702856826467507</v>
+        <v>0.04651177081121709</v>
       </c>
       <c r="W92">
-        <v>0.2247106636031896</v>
+        <v>0.224832524442715</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2351428413233753</v>
+        <v>0.2325588540560855</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2365338177649846</v>
+        <v>0.2384338177649845</v>
       </c>
       <c r="C93">
-        <v>-41.66249400376492</v>
+        <v>-42.34442871723855</v>
       </c>
       <c r="D93">
-        <v>7.901505996235088</v>
+        <v>7.823571282761456</v>
       </c>
       <c r="E93">
-        <v>36.664</v>
+        <v>37.268</v>
       </c>
       <c r="F93">
-        <v>54.96400000000001</v>
+        <v>55.568</v>
       </c>
       <c r="G93">
         <v>5.4</v>
@@ -8913,37 +8913,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M93">
-        <v>12.9605112</v>
+        <v>13.1029344</v>
       </c>
       <c r="N93">
-        <v>-9.946429567346941</v>
+        <v>-10.08885276734694</v>
       </c>
       <c r="O93">
-        <v>-1.989285913469388</v>
+        <v>-2.017770553469388</v>
       </c>
       <c r="P93">
-        <v>-7.957143653877553</v>
+        <v>-8.071082213877553</v>
       </c>
       <c r="Q93">
-        <v>-3.767143653877554</v>
+        <v>-3.881082213877553</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3548468946901541</v>
+        <v>0.3934777565264233</v>
       </c>
       <c r="T93">
-        <v>6.023899206193692</v>
+        <v>6.776886606967905</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04651177081121709</v>
+        <v>0.04600620808500822</v>
       </c>
       <c r="W93">
-        <v>0.224832524442715</v>
+        <v>0.2249517361335551</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2325588540560855</v>
+        <v>0.2300310404250411</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2384338177649845</v>
+        <v>0.2403338177649845</v>
       </c>
       <c r="C94">
-        <v>-42.34442871723855</v>
+        <v>-43.02484106347239</v>
       </c>
       <c r="D94">
-        <v>7.823571282761456</v>
+        <v>7.747158936527624</v>
       </c>
       <c r="E94">
-        <v>37.268</v>
+        <v>37.87200000000001</v>
       </c>
       <c r="F94">
-        <v>55.568</v>
+        <v>56.17200000000001</v>
       </c>
       <c r="G94">
         <v>5.4</v>
@@ -8995,37 +8995,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M94">
-        <v>13.1029344</v>
+        <v>13.2453576</v>
       </c>
       <c r="N94">
-        <v>-10.08885276734694</v>
+        <v>-10.23127596734694</v>
       </c>
       <c r="O94">
-        <v>-2.017770553469388</v>
+        <v>-2.046255193469388</v>
       </c>
       <c r="P94">
-        <v>-8.071082213877553</v>
+        <v>-8.185020773877554</v>
       </c>
       <c r="Q94">
-        <v>-3.881082213877553</v>
+        <v>-3.995020773877554</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3934777565264233</v>
+        <v>0.4431460074587696</v>
       </c>
       <c r="T94">
-        <v>6.776886606967905</v>
+        <v>7.745013265106179</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04600620808500822</v>
+        <v>0.04551151767549199</v>
       </c>
       <c r="W94">
-        <v>0.2249517361335551</v>
+        <v>0.225068384132119</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2300310404250411</v>
+        <v>0.22755758837746</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2403338177649845</v>
+        <v>0.2422338177649845</v>
       </c>
       <c r="C95">
-        <v>-43.02484106347239</v>
+        <v>-43.70377521761591</v>
       </c>
       <c r="D95">
-        <v>7.747158936527624</v>
+        <v>7.6722247823841</v>
       </c>
       <c r="E95">
-        <v>37.87200000000001</v>
+        <v>38.47600000000001</v>
       </c>
       <c r="F95">
-        <v>56.17200000000001</v>
+        <v>56.77600000000001</v>
       </c>
       <c r="G95">
         <v>5.4</v>
@@ -9077,37 +9077,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M95">
-        <v>13.2453576</v>
+        <v>13.3877808</v>
       </c>
       <c r="N95">
-        <v>-10.23127596734694</v>
+        <v>-10.37369916734694</v>
       </c>
       <c r="O95">
-        <v>-2.046255193469388</v>
+        <v>-2.074739833469388</v>
       </c>
       <c r="P95">
-        <v>-8.185020773877554</v>
+        <v>-8.298959333877553</v>
       </c>
       <c r="Q95">
-        <v>-3.995020773877554</v>
+        <v>-4.108959333877554</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4431460074587696</v>
+        <v>0.5093703420352312</v>
       </c>
       <c r="T95">
-        <v>7.745013265106179</v>
+        <v>9.035848809290544</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04551151767549199</v>
+        <v>0.04502735259383782</v>
       </c>
       <c r="W95">
-        <v>0.225068384132119</v>
+        <v>0.2251825502583731</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.22755758837746</v>
+        <v>0.2251367629691891</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2422338177649845</v>
+        <v>0.2441338177649845</v>
       </c>
       <c r="C96">
-        <v>-43.70377521761591</v>
+        <v>-44.38127366206074</v>
       </c>
       <c r="D96">
-        <v>7.6722247823841</v>
+        <v>7.598726337939275</v>
       </c>
       <c r="E96">
-        <v>38.47600000000001</v>
+        <v>39.08000000000001</v>
       </c>
       <c r="F96">
-        <v>56.77600000000001</v>
+        <v>57.38000000000001</v>
       </c>
       <c r="G96">
         <v>5.4</v>
@@ -9159,37 +9159,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M96">
-        <v>13.3877808</v>
+        <v>13.530204</v>
       </c>
       <c r="N96">
-        <v>-10.37369916734694</v>
+        <v>-10.51612236734694</v>
       </c>
       <c r="O96">
-        <v>-2.074739833469388</v>
+        <v>-2.103224473469389</v>
       </c>
       <c r="P96">
-        <v>-8.298959333877553</v>
+        <v>-8.412897893877552</v>
       </c>
       <c r="Q96">
-        <v>-4.108959333877554</v>
+        <v>-4.222897893877553</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5093703420352312</v>
+        <v>0.6020844104422777</v>
       </c>
       <c r="T96">
-        <v>9.035848809290544</v>
+        <v>10.84301857114866</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04502735259383782</v>
+        <v>0.04455338046127111</v>
       </c>
       <c r="W96">
-        <v>0.2251825502583731</v>
+        <v>0.2252943128872323</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2251367629691891</v>
+        <v>0.2227669023063555</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2441338177649845</v>
+        <v>0.2460338177649845</v>
       </c>
       <c r="C97">
-        <v>-44.38127366206074</v>
+        <v>-45.05737726675267</v>
       </c>
       <c r="D97">
-        <v>7.598726337939275</v>
+        <v>7.526622733247334</v>
       </c>
       <c r="E97">
-        <v>39.08000000000001</v>
+        <v>39.68400000000001</v>
       </c>
       <c r="F97">
-        <v>57.38000000000001</v>
+        <v>57.98400000000001</v>
       </c>
       <c r="G97">
         <v>5.4</v>
@@ -9241,37 +9241,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M97">
-        <v>13.530204</v>
+        <v>13.6726272</v>
       </c>
       <c r="N97">
-        <v>-10.51612236734694</v>
+        <v>-10.65854556734694</v>
       </c>
       <c r="O97">
-        <v>-2.103224473469389</v>
+        <v>-2.131709113469388</v>
       </c>
       <c r="P97">
-        <v>-8.412897893877552</v>
+        <v>-8.526836453877554</v>
       </c>
       <c r="Q97">
-        <v>-4.222897893877553</v>
+        <v>-4.336836453877554</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6020844104422777</v>
+        <v>0.7411555130528475</v>
       </c>
       <c r="T97">
-        <v>10.84301857114866</v>
+        <v>13.55377321393583</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04455338046127111</v>
+        <v>0.04408928274813287</v>
       </c>
       <c r="W97">
-        <v>0.2252943128872323</v>
+        <v>0.2254037471279903</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2227669023063555</v>
+        <v>0.2204464137406643</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2460338177649845</v>
+        <v>0.2479338177649845</v>
       </c>
       <c r="C98">
-        <v>-45.05737726675267</v>
+        <v>-45.73212536497439</v>
       </c>
       <c r="D98">
-        <v>7.526622733247334</v>
+        <v>7.455874635025607</v>
       </c>
       <c r="E98">
-        <v>39.684</v>
+        <v>40.288</v>
       </c>
       <c r="F98">
-        <v>57.984</v>
+        <v>58.588</v>
       </c>
       <c r="G98">
         <v>5.4</v>
@@ -9323,37 +9323,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M98">
-        <v>13.6726272</v>
+        <v>13.8150504</v>
       </c>
       <c r="N98">
-        <v>-10.65854556734694</v>
+        <v>-10.80096876734694</v>
       </c>
       <c r="O98">
-        <v>-2.131709113469388</v>
+        <v>-2.160193753469388</v>
       </c>
       <c r="P98">
-        <v>-8.526836453877552</v>
+        <v>-8.640775013877551</v>
       </c>
       <c r="Q98">
-        <v>-4.336836453877552</v>
+        <v>-4.450775013877552</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7411555130528457</v>
+        <v>0.972940684070461</v>
       </c>
       <c r="T98">
-        <v>13.55377321393579</v>
+        <v>18.07169761858106</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04408928274813288</v>
+        <v>0.0436347540600078</v>
       </c>
       <c r="W98">
-        <v>0.2254037471279903</v>
+        <v>0.2255109249926502</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2204464137406643</v>
+        <v>0.2181737703000389</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2479338177649845</v>
+        <v>0.2498338177649845</v>
       </c>
       <c r="C99">
-        <v>-45.73212536497439</v>
+        <v>-46.40555582489387</v>
       </c>
       <c r="D99">
-        <v>7.455874635025607</v>
+        <v>7.386444175106135</v>
       </c>
       <c r="E99">
-        <v>40.288</v>
+        <v>40.89200000000001</v>
       </c>
       <c r="F99">
-        <v>58.588</v>
+        <v>59.19200000000001</v>
       </c>
       <c r="G99">
         <v>5.4</v>
@@ -9405,37 +9405,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M99">
-        <v>13.8150504</v>
+        <v>13.9574736</v>
       </c>
       <c r="N99">
-        <v>-10.80096876734694</v>
+        <v>-10.94339196734694</v>
       </c>
       <c r="O99">
-        <v>-2.160193753469388</v>
+        <v>-2.188678393469388</v>
       </c>
       <c r="P99">
-        <v>-8.640775013877551</v>
+        <v>-8.754713573877552</v>
       </c>
       <c r="Q99">
-        <v>-4.450775013877552</v>
+        <v>-4.564713573877553</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.972940684070461</v>
+        <v>1.436511026105691</v>
       </c>
       <c r="T99">
-        <v>18.07169761858106</v>
+        <v>27.10754642787158</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0436347540600078</v>
+        <v>0.04318950146755873</v>
       </c>
       <c r="W99">
-        <v>0.2255109249926502</v>
+        <v>0.2256159155539497</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2181737703000389</v>
+        <v>0.2159475073377937</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2498338177649845</v>
+        <v>0.2517338177649845</v>
       </c>
       <c r="C100">
-        <v>-46.40555582489387</v>
+        <v>-47.07770511715201</v>
       </c>
       <c r="D100">
-        <v>7.386444175106135</v>
+        <v>7.318294882847991</v>
       </c>
       <c r="E100">
-        <v>40.89200000000001</v>
+        <v>41.49600000000001</v>
       </c>
       <c r="F100">
-        <v>59.19200000000001</v>
+        <v>59.79600000000001</v>
       </c>
       <c r="G100">
         <v>5.4</v>
@@ -9487,37 +9487,37 @@
         <v>3.014081632653062</v>
       </c>
       <c r="M100">
-        <v>13.9574736</v>
+        <v>14.0998968</v>
       </c>
       <c r="N100">
-        <v>-10.94339196734694</v>
+        <v>-11.08581516734694</v>
       </c>
       <c r="O100">
-        <v>-2.188678393469388</v>
+        <v>-2.217163033469388</v>
       </c>
       <c r="P100">
-        <v>-8.754713573877552</v>
+        <v>-8.868652133877552</v>
       </c>
       <c r="Q100">
-        <v>-4.564713573877553</v>
+        <v>-4.678652133877552</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.436511026105691</v>
+        <v>2.827222052211383</v>
       </c>
       <c r="T100">
-        <v>27.10754642787158</v>
+        <v>54.21509285574317</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04318950146755873</v>
+        <v>0.04275324387697733</v>
       </c>
       <c r="W100">
-        <v>0.2256159155539497</v>
+        <v>0.2257187850938087</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2159475073377937</v>
+        <v>0.2137662193848866</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2517338177649845</v>
-      </c>
-      <c r="C101">
-        <v>-47.07770511715201</v>
-      </c>
-      <c r="D101">
-        <v>7.318294882847991</v>
-      </c>
-      <c r="E101">
-        <v>41.49600000000001</v>
-      </c>
-      <c r="F101">
-        <v>59.79600000000001</v>
-      </c>
-      <c r="G101">
-        <v>5.4</v>
-      </c>
-      <c r="H101">
-        <v>42.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.204081632653061</v>
-      </c>
-      <c r="K101">
-        <v>4.19</v>
-      </c>
-      <c r="L101">
-        <v>3.014081632653062</v>
-      </c>
-      <c r="M101">
-        <v>14.0998968</v>
-      </c>
-      <c r="N101">
-        <v>-11.08581516734694</v>
-      </c>
-      <c r="O101">
-        <v>-2.217163033469388</v>
-      </c>
-      <c r="P101">
-        <v>-8.868652133877552</v>
-      </c>
-      <c r="Q101">
-        <v>-4.678652133877552</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.827222052211383</v>
-      </c>
-      <c r="T101">
-        <v>54.21509285574317</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04275324387697733</v>
-      </c>
-      <c r="W101">
-        <v>0.2257187850938087</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2137662193848866</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
